--- a/VerveStacks_DEU_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2176EB12-552F-4763-BEAC-C50FB559670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D064A20C-8812-4C3F-A4B0-E024F8FC2ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2069" uniqueCount="533">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -879,16 +879,82 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_DEU_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_DEU_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_DEU_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_solelc_spv_DEU_008</t>
@@ -897,46 +963,52 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_solelc_spv_DEU_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_DEU_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_solelc_spv_DEU_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_DEU_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_DEU_019</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_DEU_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
+    <t>distr_solelc_spv_DEU_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_solelc_spv_DEU_022</t>
@@ -945,148 +1017,157 @@
     <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_solelc_spv_DEU_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_DEU_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_DEU_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_DEU_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_w24839976-380_DEU,e_w88916034-380_DEU,e_w42410916-380_DEU,e_w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w1094015892-380_DEU,e_w170123812-400_DEU</t>
-  </si>
-  <si>
-    <t>e_w24839976-380_DEU,e_w952346322-380_DEU,e_w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w29309786-380_DEU,e_w26472665-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w952346322-380_DEU,e_w1128250704-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w525964617_DEU</t>
-  </si>
-  <si>
-    <t>e_w1094015892-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w42410916-380_DEU,e_w24757392-380_DEU,e_w29309786-380_DEU,e_w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w24757392-380_DEU,e_w157328339-380_DEU</t>
+    <t>e_w170123812-400_DEU,e_w157328339-380_DEU,e_w952346322-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w952346322-380_DEU,e_w26472665-380_DEU,e_w1128250707-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w68532663-220_DEU,e_w29084374-380_DEU,e_DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>e_w940919943_DEU,e_w525964617_DEU,e_w170123812-400_DEU</t>
+  </si>
+  <si>
+    <t>e_w952346322-380_DEU,e_w1128250707-380_DEU,e_w525964617_DEU</t>
+  </si>
+  <si>
+    <t>e_w136015463-225_DEU,e_w29084374-380_DEU,e_w157328339-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w143882655-380_DEU,e_w26472665-380_DEU,e_w1128250707-380_DEU,e_w157328339-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w26472665-380_DEU,e_w940919943_DEU,e_w525964617_DEU</t>
+  </si>
+  <si>
+    <t>e_w108797675-380_DEU,e_w1128250707-380_DEU,e_w143882655-380_DEU,e_w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w525964617_DEU,e_w1128250707-380_DEU,e_w275466323_DEU</t>
+  </si>
+  <si>
+    <t>e_DE173-220_DEU,e_w108797675-380_DEU,e_w136015463-225_DEU</t>
+  </si>
+  <si>
+    <t>e_w108797675-380_DEU,e_w68532663-220_DEU,e_w143882655-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w940919943_DEU,e_w170123812-400_DEU</t>
+  </si>
+  <si>
+    <t>e_DE173-220_DEU,e_w870598507_DEU,e_w136015463-225_DEU,e_w108797675-380_DEU,e_w29084374-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w136015463-225_DEU,e_w143882655-380_DEU,e_w870598507_DEU,e_w157328339-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w170123812-400_DEU,e_w1128250707-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w870598507_DEU,e_w952346322-380_DEU,e_w157328339-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w525964617_DEU,e_w449010725-380_DEU,e_w275466323_DEU</t>
+  </si>
+  <si>
+    <t>e_w68532663-220_DEU</t>
+  </si>
+  <si>
+    <t>e_w143882655-380_DEU,e_w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>e_DE173-220_DEU,e_w108797675-380_DEU</t>
   </si>
   <si>
     <t>e_w952346322-380_DEU</t>
   </si>
   <si>
-    <t>e_w42488850-380_DEU,e_w1128250704-380_DEU,e_w29309786-380_DEU,e_w525964617_DEU</t>
-  </si>
-  <si>
-    <t>e_w525964617_DEU,e_w1094015892-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w24839976-380_DEU,e_w42488850-380_DEU,e_w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w952346322-380_DEU,e_w1128250704-380_DEU,e_w525964617_DEU</t>
-  </si>
-  <si>
-    <t>e_w24839976-380_DEU,e_w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w76246159-380_DEU,e_w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w157328339-380_DEU,e_w170123812-400_DEU</t>
-  </si>
-  <si>
-    <t>e_w29309786-380_DEU,e_w24757392-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w24757392-380_DEU,e_w26472665-380_DEU,e_w157328339-380_DEU</t>
+    <t>e_w68532663-220_DEU,e_DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_DEU_014</t>
@@ -1095,243 +1176,216 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_wonelc_won_DEU_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_DEU_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_DEU_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_DEU_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_DEU_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_DEU_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_DEU_013</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_DEU_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_DEU_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_DEU_012</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>elc_won_DEU_017</t>
+  </si>
+  <si>
+    <t>e_DE173-220_DEU,e_w108797675-380_DEU,e_w29084374-380_DEU,e_w143882655-380_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_005</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_022</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_020</t>
+  </si>
+  <si>
+    <t>e_DE173-220_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_010</t>
+  </si>
+  <si>
+    <t>e_w1128250707-380_DEU,e_w143882655-380_DEU,e_w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_001</t>
+  </si>
+  <si>
+    <t>e_w26472665-380_DEU,e_w940919943_DEU,e_w1128250707-380_DEU,e_w525964617_DEU,e_w170123812-400_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_021</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_003</t>
+  </si>
+  <si>
+    <t>e_w26472665-380_DEU,e_w157328339-380_DEU,e_w952346322-380_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_011</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_006</t>
+  </si>
+  <si>
+    <t>e_w525964617_DEU,e_w449010725-380_DEU,e_w275466323_DEU,e_w940919943_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_019</t>
+  </si>
+  <si>
+    <t>e_w108797675-380_DEU,e_w68532663-220_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_002</t>
+  </si>
+  <si>
+    <t>e_w136015463-225_DEU,e_w143882655-380_DEU,e_w157328339-380_DEU,e_w870598507_DEU,e_w26472665-380_DEU</t>
+  </si>
+  <si>
     <t>elc_won_DEU_014</t>
   </si>
   <si>
-    <t>e_w157328339-380_DEU</t>
+    <t>e_DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_015</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_018</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_007</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_009</t>
+  </si>
+  <si>
+    <t>e_w1128250707-380_DEU,e_w525964617_DEU,e_w26472665-380_DEU,e_w275466323_DEU</t>
+  </si>
+  <si>
+    <t>elc_won_DEU_016</t>
+  </si>
+  <si>
+    <t>e_w108797675-380_DEU,e_w143882655-380_DEU</t>
   </si>
   <si>
     <t>elc_won_DEU_008</t>
   </si>
   <si>
-    <t>elc_won_DEU_009</t>
-  </si>
-  <si>
-    <t>e_w1128250704-380_DEU,e_w525964617_DEU,e_w26472665-380_DEU,e_w1094015892-380_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_019</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_002</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_003</t>
-  </si>
-  <si>
-    <t>e_w26472665-380_DEU,e_w24757392-380_DEU,e_w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_021</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_015</t>
+    <t>e_DE173-220_DEU,e_w870598507_DEU,e_w952346322-380_DEU,e_w136015463-225_DEU,e_w157328339-380_DEU</t>
   </si>
   <si>
     <t>elc_won_DEU_004</t>
   </si>
   <si>
-    <t>elc_won_DEU_020</t>
-  </si>
-  <si>
-    <t>e_w88916034-380_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_006</t>
+    <t>e_w170123812-400_DEU,e_w952346322-380_DEU,e_w1128250707-380_DEU,e_w525964617_DEU,e_w449010725-380_DEU</t>
   </si>
   <si>
     <t>elc_won_DEU_013</t>
   </si>
   <si>
-    <t>elc_won_DEU_001</t>
-  </si>
-  <si>
-    <t>e_w26472665-380_DEU,e_w1094015892-380_DEU,e_w157328339-380_DEU,e_w170123812-400_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_005</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_022</t>
-  </si>
-  <si>
-    <t>e_w88916034-380_DEU,e_w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_017</t>
-  </si>
-  <si>
-    <t>e_w24839976-380_DEU,e_w42410916-380_DEU,e_w29309786-380_DEU,e_w24757392-380_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_018</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_011</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_016</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_007</t>
-  </si>
-  <si>
-    <t>e_w952346322-380_DEU,e_w42488850-380_DEU,e_w1128250704-380_DEU</t>
-  </si>
-  <si>
-    <t>elc_won_DEU_010</t>
-  </si>
-  <si>
-    <t>e_w29309786-380_DEU,e_w26472665-380_DEU,e_w24757392-380_DEU</t>
-  </si>
-  <si>
     <t>elc_won_DEU_012</t>
   </si>
   <si>
+    <t>e_w136015463-225_DEU,e_w29084374-380_DEU</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_DEU_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_DEU_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_DEU_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_DEU_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_DEU_002</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_DEU_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_DEU_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_DEU_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_DEU_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_DEU_010</t>
   </si>
   <si>
@@ -1344,72 +1398,51 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_DEU_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_DEU_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_DEU_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_DEU_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_DEU_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_DEU_009</t>
+  </si>
+  <si>
+    <t>e_w525964617_DEU,e_w940919943_DEU</t>
+  </si>
+  <si>
+    <t>elc_wof_DEU_007</t>
+  </si>
+  <si>
+    <t>e_w1128250707-380_DEU,e_w525964617_DEU</t>
+  </si>
+  <si>
+    <t>elc_wof_DEU_001</t>
+  </si>
+  <si>
+    <t>elc_wof_DEU_004</t>
   </si>
   <si>
     <t>elc_wof_DEU_002</t>
   </si>
   <si>
-    <t>e_w1128250704-380_DEU,e_w525964617_DEU</t>
-  </si>
-  <si>
-    <t>elc_wof_DEU_001</t>
+    <t>e_w1128250707-380_DEU,e_w449010725-380_DEU</t>
   </si>
   <si>
     <t>elc_wof_DEU_003</t>
   </si>
   <si>
+    <t>elc_wof_DEU_008</t>
+  </si>
+  <si>
+    <t>elc_wof_DEU_005</t>
+  </si>
+  <si>
     <t>elc_wof_DEU_010</t>
   </si>
   <si>
+    <t>e_w275466323_DEU,e_w940919943_DEU</t>
+  </si>
+  <si>
     <t>elc_wof_DEU_006</t>
   </si>
   <si>
     <t>e_w170123812-400_DEU</t>
   </si>
   <si>
-    <t>elc_wof_DEU_004</t>
-  </si>
-  <si>
-    <t>elc_wof_DEU_009</t>
-  </si>
-  <si>
-    <t>elc_wof_DEU_007</t>
-  </si>
-  <si>
-    <t>elc_wof_DEU_008</t>
-  </si>
-  <si>
-    <t>elc_wof_DEU_005</t>
-  </si>
-  <si>
     <t>e_won_DEU_001</t>
   </si>
   <si>
@@ -1602,73 +1635,94 @@
     <t>wind offshore resource in cluster 10</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS</t>
+    <t>en_gas_ccgt</t>
+  </si>
+  <si>
+    <t>ncap_cost</t>
+  </si>
+  <si>
+    <t>ncap_fom</t>
+  </si>
+  <si>
+    <t>act_cost</t>
+  </si>
+  <si>
+    <t>ncap_tlife</t>
+  </si>
+  <si>
+    <t>ncap_iled</t>
+  </si>
+  <si>
+    <t>en_gas_turbine</t>
+  </si>
+  <si>
+    <t>en_gas_chp</t>
+  </si>
+  <si>
+    <t>ELC,HET</t>
+  </si>
+  <si>
+    <t>ncap_chpr</t>
+  </si>
+  <si>
+    <t>en_gas_fuelcell</t>
+  </si>
+  <si>
+    <t>en_gas_ccs</t>
+  </si>
+  <si>
+    <t>ELC,CO2Cap</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical</t>
+  </si>
+  <si>
+    <t>en_coal_igcc</t>
+  </si>
+  <si>
+    <t>en_coal_ccs</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_ccs</t>
+  </si>
+  <si>
+    <t>en_coal_oxyfuel_ccs</t>
+  </si>
+  <si>
+    <t>en_nuclear</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr</t>
+  </si>
+  <si>
+    <t>en_biomass</t>
   </si>
   <si>
     <t>ncap_af</t>
   </si>
   <si>
-    <t>ncap_cost</t>
-  </si>
-  <si>
-    <t>ncap_fom</t>
-  </si>
-  <si>
-    <t>ncap_iled</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit</t>
-  </si>
-  <si>
-    <t>CCGT</t>
-  </si>
-  <si>
-    <t>CCGT + CCS</t>
-  </si>
-  <si>
-    <t>Coal + CCS</t>
-  </si>
-  <si>
-    <t>Gas turbine</t>
-  </si>
-  <si>
-    <t>Hydropower - large-scale unit</t>
-  </si>
-  <si>
-    <t>IGCC</t>
-  </si>
-  <si>
-    <t>IGCC + CCS</t>
-  </si>
-  <si>
-    <t>Nuclear large</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS</t>
-  </si>
-  <si>
-    <t>Solar photovoltaics - Large scale unit</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL</t>
-  </si>
-  <si>
-    <t>Wind offshore</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>Wind onshore</t>
+    <t>en_biomass_cofiring</t>
+  </si>
+  <si>
+    <t>en_biomass_chp</t>
+  </si>
+  <si>
+    <t>en_biomass_ccs</t>
+  </si>
+  <si>
+    <t>en_geothermal</t>
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>CHP</t>
   </si>
   <si>
     <t>e_DE62-380_DEU,e_w170123812-400_DEU,e_w59026005-380_DEU,e_w952346322-380_DEU</t>
@@ -2625,6 +2679,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -3602,7 +3659,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -6403,7 +6460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20BFCD0-4064-44B3-BFA6-437E2D2CB670}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{974E8F4D-7359-4A67-832F-B7BE9872F561}">
   <dimension ref="B9:BD33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6608,10 +6665,10 @@
         <v>225</v>
       </c>
       <c r="L11">
-        <v>13.938003670888978</v>
+        <v>13.335303670888978</v>
       </c>
       <c r="M11">
-        <v>0.1557223752417688</v>
+        <v>0.15569184210407869</v>
       </c>
       <c r="O11" t="s">
         <v>249</v>
@@ -6641,25 +6698,25 @@
         <v>250</v>
       </c>
       <c r="Y11" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Z11" t="s">
         <v>300</v>
       </c>
       <c r="AA11">
-        <v>0.99845115321674904</v>
+        <v>0.99878112008644837</v>
       </c>
       <c r="AB11">
-        <v>28.395524359600802</v>
+        <v>22.346131748445966</v>
       </c>
       <c r="AD11" t="s">
         <v>249</v>
       </c>
       <c r="AE11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AF11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6674,28 +6731,28 @@
         <v>176</v>
       </c>
       <c r="AL11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AM11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO11">
-        <v>0.99667925950575054</v>
+        <v>0.99863966972203233</v>
       </c>
       <c r="AP11">
-        <v>60.880242394574381</v>
+        <v>24.939388429407202</v>
       </c>
       <c r="AR11" t="s">
         <v>249</v>
       </c>
       <c r="AS11" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AT11" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6710,19 +6767,19 @@
         <v>176</v>
       </c>
       <c r="AZ11" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="BA11" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="BB11" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="BC11">
-        <v>0.99345136660650646</v>
+        <v>0.99726555940500838</v>
       </c>
       <c r="BD11">
-        <v>120.05827888071518</v>
+        <v>50.131410908180094</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6754,10 +6811,10 @@
         <v>226</v>
       </c>
       <c r="L12">
-        <v>18.31863654586293</v>
+        <v>17.31563654586293</v>
       </c>
       <c r="M12">
-        <v>0.1400600677372365</v>
+        <v>0.1399707576850984</v>
       </c>
       <c r="O12" t="s">
         <v>249</v>
@@ -6787,25 +6844,25 @@
         <v>254</v>
       </c>
       <c r="Y12" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="Z12" t="s">
         <v>301</v>
       </c>
       <c r="AA12">
-        <v>0.99854052945036897</v>
+        <v>0.99888062191104332</v>
       </c>
       <c r="AB12">
-        <v>26.756960076568774</v>
+        <v>20.521931630871453</v>
       </c>
       <c r="AD12" t="s">
         <v>249</v>
       </c>
       <c r="AE12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AF12" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -6820,28 +6877,28 @@
         <v>176</v>
       </c>
       <c r="AL12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AM12" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AN12" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="AO12">
-        <v>0.99888649626708259</v>
+        <v>0.9974914420479265</v>
       </c>
       <c r="AP12">
-        <v>20.414235103486192</v>
+        <v>45.990229121347099</v>
       </c>
       <c r="AR12" t="s">
         <v>249</v>
       </c>
       <c r="AS12" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AT12" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -6856,19 +6913,19 @@
         <v>176</v>
       </c>
       <c r="AZ12" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="BA12" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="BB12" t="s">
-        <v>304</v>
+        <v>426</v>
       </c>
       <c r="BC12">
-        <v>0.98635566783526007</v>
+        <v>0.99871075555058875</v>
       </c>
       <c r="BD12">
-        <v>250.14608968689959</v>
+        <v>23.636148239206339</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6900,10 +6957,10 @@
         <v>227</v>
       </c>
       <c r="L13">
-        <v>30.238043484360141</v>
+        <v>27.385443484360142</v>
       </c>
       <c r="M13">
-        <v>0.14975968217471289</v>
+        <v>0.1497197051444458</v>
       </c>
       <c r="O13" t="s">
         <v>249</v>
@@ -6933,25 +6990,25 @@
         <v>256</v>
       </c>
       <c r="Y13" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="Z13" t="s">
         <v>302</v>
       </c>
       <c r="AA13">
-        <v>0.99902896095987681</v>
+        <v>0.99778386838567956</v>
       </c>
       <c r="AB13">
-        <v>17.802382402257905</v>
+        <v>40.629079595875325</v>
       </c>
       <c r="AD13" t="s">
         <v>249</v>
       </c>
       <c r="AE13" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AF13" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -6966,28 +7023,28 @@
         <v>176</v>
       </c>
       <c r="AL13" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AM13" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN13" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="AO13">
-        <v>0.99840287720275267</v>
+        <v>0.99888991682459083</v>
       </c>
       <c r="AP13">
-        <v>29.280584616200382</v>
+        <v>20.351524882501383</v>
       </c>
       <c r="AR13" t="s">
         <v>249</v>
       </c>
       <c r="AS13" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AT13" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -7002,19 +7059,19 @@
         <v>176</v>
       </c>
       <c r="AZ13" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="BA13" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="BB13" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="BC13">
-        <v>0.99374840656294539</v>
+        <v>0.98632175834146862</v>
       </c>
       <c r="BD13">
-        <v>114.61254634600208</v>
+        <v>250.7677637397411</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7046,10 +7103,10 @@
         <v>228</v>
       </c>
       <c r="L14">
-        <v>45.351574205977535</v>
+        <v>41.481174205977538</v>
       </c>
       <c r="M14">
-        <v>0.14146464867513009</v>
+        <v>0.14143979365621501</v>
       </c>
       <c r="O14" t="s">
         <v>249</v>
@@ -7079,25 +7136,25 @@
         <v>258</v>
       </c>
       <c r="Y14" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="Z14" t="s">
         <v>303</v>
       </c>
       <c r="AA14">
-        <v>0.99837540256192037</v>
+        <v>0.99784429564758459</v>
       </c>
       <c r="AB14">
-        <v>29.784286364794184</v>
+        <v>39.521246460948468</v>
       </c>
       <c r="AD14" t="s">
         <v>249</v>
       </c>
       <c r="AE14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AF14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7112,28 +7169,28 @@
         <v>176</v>
       </c>
       <c r="AL14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AM14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AN14" t="s">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="AO14">
-        <v>0.99835510064157384</v>
+        <v>0.99912192348268269</v>
       </c>
       <c r="AP14">
-        <v>30.156488237812564</v>
+        <v>16.098069484150571</v>
       </c>
       <c r="AR14" t="s">
         <v>249</v>
       </c>
       <c r="AS14" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AT14" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7148,19 +7205,19 @@
         <v>176</v>
       </c>
       <c r="AZ14" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="BA14" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="BB14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="BC14">
-        <v>0.99861480954449533</v>
+        <v>0.99732398652587073</v>
       </c>
       <c r="BD14">
-        <v>25.395158350918766</v>
+        <v>49.060247025704001</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7192,10 +7249,10 @@
         <v>229</v>
       </c>
       <c r="L15">
-        <v>34.531914591504368</v>
+        <v>32.727714591504373</v>
       </c>
       <c r="M15">
-        <v>0.15529591554537989</v>
+        <v>0.15523620412698039</v>
       </c>
       <c r="O15" t="s">
         <v>249</v>
@@ -7225,25 +7282,25 @@
         <v>260</v>
       </c>
       <c r="Y15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z15" t="s">
         <v>304</v>
       </c>
       <c r="AA15">
-        <v>0.99797139203037322</v>
+        <v>0.99873044108599873</v>
       </c>
       <c r="AB15">
-        <v>37.191146109824579</v>
+        <v>23.275246756689327</v>
       </c>
       <c r="AD15" t="s">
         <v>249</v>
       </c>
       <c r="AE15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AF15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7258,28 +7315,28 @@
         <v>176</v>
       </c>
       <c r="AL15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM15" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN15" t="s">
-        <v>308</v>
+        <v>374</v>
       </c>
       <c r="AO15">
-        <v>0.99851446571821256</v>
+        <v>0.99832201252102326</v>
       </c>
       <c r="AP15">
-        <v>27.234795166103936</v>
+        <v>30.76310378124024</v>
       </c>
       <c r="AR15" t="s">
         <v>249</v>
       </c>
       <c r="AS15" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AT15" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7294,19 +7351,19 @@
         <v>176</v>
       </c>
       <c r="AZ15" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="BA15" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="BB15" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="BC15">
-        <v>0.99845350558031343</v>
+        <v>0.99347066760081382</v>
       </c>
       <c r="BD15">
-        <v>28.352397694253892</v>
+        <v>119.7044273184132</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7338,10 +7395,10 @@
         <v>230</v>
       </c>
       <c r="L16">
-        <v>38.190379780391297</v>
+        <v>37.2056797803913</v>
       </c>
       <c r="M16">
-        <v>0.14992284072312301</v>
+        <v>0.1499321031847301</v>
       </c>
       <c r="O16" t="s">
         <v>249</v>
@@ -7371,25 +7428,25 @@
         <v>262</v>
       </c>
       <c r="Y16" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="Z16" t="s">
         <v>305</v>
       </c>
       <c r="AA16">
-        <v>0.99792185696155833</v>
+        <v>0.99784395027301009</v>
       </c>
       <c r="AB16">
-        <v>38.099289038098078</v>
+        <v>39.527578328149289</v>
       </c>
       <c r="AD16" t="s">
         <v>249</v>
       </c>
       <c r="AE16" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AF16" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7404,28 +7461,28 @@
         <v>176</v>
       </c>
       <c r="AL16" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AM16" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AN16" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AO16">
-        <v>0.99838078830661203</v>
+        <v>0.99853059324545101</v>
       </c>
       <c r="AP16">
-        <v>29.68554771211182</v>
+        <v>26.939123833397286</v>
       </c>
       <c r="AR16" t="s">
         <v>249</v>
       </c>
       <c r="AS16" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AT16" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7440,19 +7497,19 @@
         <v>176</v>
       </c>
       <c r="AZ16" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="BA16" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="BB16" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="BC16">
-        <v>0.99731983040343442</v>
+        <v>0.99389340181257835</v>
       </c>
       <c r="BD16">
-        <v>49.136442603701539</v>
+        <v>111.95430010272941</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7484,10 +7541,10 @@
         <v>231</v>
       </c>
       <c r="L17">
-        <v>13.44361680351453</v>
+        <v>12.590316803514531</v>
       </c>
       <c r="M17">
-        <v>0.1366658191416176</v>
+        <v>0.1365808536581983</v>
       </c>
       <c r="O17" t="s">
         <v>249</v>
@@ -7517,25 +7574,25 @@
         <v>264</v>
       </c>
       <c r="Y17" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Z17" t="s">
         <v>306</v>
       </c>
       <c r="AA17">
-        <v>0.99839933473711795</v>
+        <v>0.99833802793673698</v>
       </c>
       <c r="AB17">
-        <v>29.345529819503312</v>
+        <v>30.469487826488972</v>
       </c>
       <c r="AD17" t="s">
         <v>249</v>
       </c>
       <c r="AE17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AF17" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7550,28 +7607,28 @@
         <v>176</v>
       </c>
       <c r="AL17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AM17" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AN17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AO17">
-        <v>0.99798110605540413</v>
+        <v>0.99798107363551802</v>
       </c>
       <c r="AP17">
-        <v>37.013055650923285</v>
+        <v>37.013650015503671</v>
       </c>
       <c r="AR17" t="s">
         <v>249</v>
       </c>
       <c r="AS17" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AT17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7586,19 +7643,19 @@
         <v>176</v>
       </c>
       <c r="AZ17" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="BA17" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="BB17" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="BC17">
-        <v>0.99726555940500838</v>
+        <v>0.99733561350881073</v>
       </c>
       <c r="BD17">
-        <v>50.131410908180094</v>
+        <v>48.847085671804372</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7630,10 +7687,10 @@
         <v>232</v>
       </c>
       <c r="L18">
-        <v>15.833691242733796</v>
+        <v>13.990791242733795</v>
       </c>
       <c r="M18">
-        <v>0.14358906321016071</v>
+        <v>0.1433723117927479</v>
       </c>
       <c r="O18" t="s">
         <v>249</v>
@@ -7663,25 +7720,25 @@
         <v>266</v>
       </c>
       <c r="Y18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Z18" t="s">
         <v>307</v>
       </c>
       <c r="AA18">
-        <v>0.99828989494874287</v>
+        <v>0.99838929994220738</v>
       </c>
       <c r="AB18">
-        <v>31.351925939714036</v>
+        <v>29.529501059531341</v>
       </c>
       <c r="AD18" t="s">
         <v>249</v>
       </c>
       <c r="AE18" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AF18" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7696,28 +7753,28 @@
         <v>176</v>
       </c>
       <c r="AL18" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AM18" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AN18" t="s">
-        <v>314</v>
+        <v>379</v>
       </c>
       <c r="AO18">
-        <v>0.99853436339984547</v>
+        <v>0.99836404262424061</v>
       </c>
       <c r="AP18">
-        <v>26.870004336166144</v>
+        <v>29.992551888922765</v>
       </c>
       <c r="AR18" t="s">
         <v>249</v>
       </c>
       <c r="AS18" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AT18" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7732,19 +7789,19 @@
         <v>176</v>
       </c>
       <c r="AZ18" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="BA18" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="BB18" t="s">
-        <v>416</v>
+        <v>312</v>
       </c>
       <c r="BC18">
-        <v>0.99871075555058875</v>
+        <v>0.9955316809931446</v>
       </c>
       <c r="BD18">
-        <v>23.636148239206339</v>
+        <v>81.919181792349548</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7776,10 +7833,10 @@
         <v>233</v>
       </c>
       <c r="L19">
-        <v>11.346394535605524</v>
+        <v>9.8698945356055265</v>
       </c>
       <c r="M19">
-        <v>0.1499023145001758</v>
+        <v>0.14992280530148369</v>
       </c>
       <c r="O19" t="s">
         <v>249</v>
@@ -7809,25 +7866,25 @@
         <v>268</v>
       </c>
       <c r="Y19" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="Z19" t="s">
         <v>308</v>
       </c>
       <c r="AA19">
-        <v>0.99783379528973448</v>
+        <v>0.99845317609837081</v>
       </c>
       <c r="AB19">
-        <v>39.713753021534231</v>
+        <v>28.358438196534451</v>
       </c>
       <c r="AD19" t="s">
         <v>249</v>
       </c>
       <c r="AE19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AF19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -7842,28 +7899,28 @@
         <v>176</v>
       </c>
       <c r="AL19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AM19" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AN19" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AO19">
-        <v>0.9982655473126083</v>
+        <v>0.99664078053750105</v>
       </c>
       <c r="AP19">
-        <v>31.798299268848115</v>
+        <v>61.585690145814638</v>
       </c>
       <c r="AR19" t="s">
         <v>249</v>
       </c>
       <c r="AS19" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AT19" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -7878,19 +7935,19 @@
         <v>176</v>
       </c>
       <c r="AZ19" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="BA19" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="BB19" t="s">
-        <v>305</v>
+        <v>435</v>
       </c>
       <c r="BC19">
-        <v>0.99733561350881073</v>
+        <v>0.99861480954449533</v>
       </c>
       <c r="BD19">
-        <v>48.847085671804372</v>
+        <v>25.395158350918766</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7922,10 +7979,10 @@
         <v>234</v>
       </c>
       <c r="L20">
-        <v>32.21637396151899</v>
+        <v>29.575673961518987</v>
       </c>
       <c r="M20">
-        <v>0.1350842179254034</v>
+        <v>0.13510612570294059</v>
       </c>
       <c r="O20" t="s">
         <v>249</v>
@@ -7955,25 +8012,25 @@
         <v>270</v>
       </c>
       <c r="Y20" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="Z20" t="s">
         <v>309</v>
       </c>
       <c r="AA20">
-        <v>0.9981906651950686</v>
+        <v>0.99815200793499381</v>
       </c>
       <c r="AB20">
-        <v>33.171138090409563</v>
+        <v>33.879854525114247</v>
       </c>
       <c r="AD20" t="s">
         <v>249</v>
       </c>
       <c r="AE20" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AF20" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -7988,28 +8045,28 @@
         <v>176</v>
       </c>
       <c r="AL20" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM20" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN20" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AO20">
-        <v>0.99912192348268269</v>
+        <v>0.99814826057016071</v>
       </c>
       <c r="AP20">
-        <v>16.098069484150571</v>
+        <v>33.948556213719677</v>
       </c>
       <c r="AR20" t="s">
         <v>249</v>
       </c>
       <c r="AS20" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AT20" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -8024,19 +8081,19 @@
         <v>176</v>
       </c>
       <c r="AZ20" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="BA20" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="BB20" t="s">
-        <v>301</v>
+        <v>437</v>
       </c>
       <c r="BC20">
-        <v>0.9955056076869333</v>
+        <v>0.99845350558031343</v>
       </c>
       <c r="BD20">
-        <v>82.397192406223127</v>
+        <v>28.352397694253892</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8068,10 +8125,10 @@
         <v>235</v>
       </c>
       <c r="L21">
-        <v>30.007867954603132</v>
+        <v>26.631067954603139</v>
       </c>
       <c r="M21">
-        <v>0.13508614213617659</v>
+        <v>0.13504969672549391</v>
       </c>
       <c r="O21" t="s">
         <v>249</v>
@@ -8101,25 +8158,25 @@
         <v>272</v>
       </c>
       <c r="Y21" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="Z21" t="s">
         <v>310</v>
       </c>
       <c r="AA21">
-        <v>0.99887966592548594</v>
+        <v>0.99844746021192377</v>
       </c>
       <c r="AB21">
-        <v>20.53945803275866</v>
+        <v>28.46322944806516</v>
       </c>
       <c r="AD21" t="s">
         <v>249</v>
       </c>
       <c r="AE21" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AF21" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8134,19 +8191,19 @@
         <v>176</v>
       </c>
       <c r="AL21" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM21" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AN21" t="s">
-        <v>311</v>
+        <v>384</v>
       </c>
       <c r="AO21">
-        <v>0.99810796133130941</v>
+        <v>0.99835967973352524</v>
       </c>
       <c r="AP21">
-        <v>34.687375592660409</v>
+        <v>30.072538218704278</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8178,10 +8235,10 @@
         <v>236</v>
       </c>
       <c r="L22">
-        <v>38.24309918267349</v>
+        <v>35.582699182673487</v>
       </c>
       <c r="M22">
-        <v>0.13439514464711891</v>
+        <v>0.1343088904178783</v>
       </c>
       <c r="O22" t="s">
         <v>249</v>
@@ -8211,25 +8268,25 @@
         <v>274</v>
       </c>
       <c r="Y22" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="Z22" t="s">
         <v>311</v>
       </c>
       <c r="AA22">
-        <v>0.99815762041917688</v>
+        <v>0.99829255692133323</v>
       </c>
       <c r="AB22">
-        <v>33.776958981757815</v>
+        <v>31.303123108890297</v>
       </c>
       <c r="AD22" t="s">
         <v>249</v>
       </c>
       <c r="AE22" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AF22" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8244,19 +8301,19 @@
         <v>176</v>
       </c>
       <c r="AL22" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AM22" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AN22" t="s">
-        <v>316</v>
+        <v>386</v>
       </c>
       <c r="AO22">
-        <v>0.99821483672858236</v>
+        <v>0.99850513569416577</v>
       </c>
       <c r="AP22">
-        <v>32.727993309323963</v>
+        <v>27.405845606960774</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8288,10 +8345,10 @@
         <v>237</v>
       </c>
       <c r="L23">
-        <v>0.95743993217852441</v>
+        <v>0.84451041346734823</v>
       </c>
       <c r="M23">
-        <v>0.1497995747391499</v>
+        <v>0.14948106200378089</v>
       </c>
       <c r="O23" t="s">
         <v>249</v>
@@ -8321,25 +8378,25 @@
         <v>276</v>
       </c>
       <c r="Y23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Z23" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="AA23">
-        <v>0.99786441593591435</v>
+        <v>0.99862957890712156</v>
       </c>
       <c r="AB23">
-        <v>39.152374508236058</v>
+        <v>25.12438670277043</v>
       </c>
       <c r="AD23" t="s">
         <v>249</v>
       </c>
       <c r="AE23" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AF23" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8354,19 +8411,19 @@
         <v>176</v>
       </c>
       <c r="AL23" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AM23" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="AN23" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="AO23">
-        <v>0.99852500850690518</v>
+        <v>0.99667925950575054</v>
       </c>
       <c r="AP23">
-        <v>27.041510706738034</v>
+        <v>60.880242394574381</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8398,10 +8455,10 @@
         <v>238</v>
       </c>
       <c r="L24">
-        <v>15.746380528104394</v>
+        <v>15.3590805281044</v>
       </c>
       <c r="M24">
-        <v>0.1361753774721691</v>
+        <v>0.13610619860759021</v>
       </c>
       <c r="O24" t="s">
         <v>249</v>
@@ -8434,22 +8491,22 @@
         <v>241</v>
       </c>
       <c r="Z24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA24">
-        <v>0.99903141795748496</v>
+        <v>0.99903622994838936</v>
       </c>
       <c r="AB24">
-        <v>17.757337446108838</v>
+        <v>17.669117612860767</v>
       </c>
       <c r="AD24" t="s">
         <v>249</v>
       </c>
       <c r="AE24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AF24" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8464,19 +8521,19 @@
         <v>176</v>
       </c>
       <c r="AL24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AM24" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="AN24" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="AO24">
-        <v>0.99753724381235709</v>
+        <v>0.99852286130979373</v>
       </c>
       <c r="AP24">
-        <v>45.150530106787691</v>
+        <v>27.080875987115267</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8508,10 +8565,10 @@
         <v>239</v>
       </c>
       <c r="L25">
-        <v>32.685256480874017</v>
+        <v>32.318456480874012</v>
       </c>
       <c r="M25">
-        <v>0.13680478137029231</v>
+        <v>0.13676871213750491</v>
       </c>
       <c r="O25" t="s">
         <v>249</v>
@@ -8541,25 +8598,25 @@
         <v>280</v>
       </c>
       <c r="Y25" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="Z25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA25">
-        <v>0.99872758352859059</v>
+        <v>0.99850143916872702</v>
       </c>
       <c r="AB25">
-        <v>23.327635309172347</v>
+        <v>27.473615240005458</v>
       </c>
       <c r="AD25" t="s">
         <v>249</v>
       </c>
       <c r="AE25" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AF25" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8574,19 +8631,19 @@
         <v>176</v>
       </c>
       <c r="AL25" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AM25" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AN25" t="s">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="AO25">
-        <v>0.99888703680442148</v>
+        <v>0.99798016544303569</v>
       </c>
       <c r="AP25">
-        <v>20.404325252272194</v>
+        <v>37.03030021101177</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8618,10 +8675,10 @@
         <v>240</v>
       </c>
       <c r="L26">
-        <v>13.348518217290337</v>
+        <v>11.840277860221624</v>
       </c>
       <c r="M26">
-        <v>0.14595055475480129</v>
+        <v>0.1459530499599051</v>
       </c>
       <c r="O26" t="s">
         <v>249</v>
@@ -8651,25 +8708,25 @@
         <v>282</v>
       </c>
       <c r="Y26" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Z26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA26">
-        <v>0.99905448261210317</v>
+        <v>0.9980849285302279</v>
       </c>
       <c r="AB26">
-        <v>17.334485444775215</v>
+        <v>35.109643612489457</v>
       </c>
       <c r="AD26" t="s">
         <v>249</v>
       </c>
       <c r="AE26" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AF26" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -8684,19 +8741,19 @@
         <v>176</v>
       </c>
       <c r="AL26" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AM26" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AN26" t="s">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="AO26">
-        <v>0.99864092836530338</v>
+        <v>0.99854534642400483</v>
       </c>
       <c r="AP26">
-        <v>24.916313302771705</v>
+        <v>26.668648893245077</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8728,10 +8785,10 @@
         <v>241</v>
       </c>
       <c r="L27">
-        <v>19.75277137741244</v>
+        <v>19.159971377412443</v>
       </c>
       <c r="M27">
-        <v>0.13638324455665041</v>
+        <v>0.13636834552397939</v>
       </c>
       <c r="O27" t="s">
         <v>249</v>
@@ -8761,25 +8818,25 @@
         <v>284</v>
       </c>
       <c r="Y27" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AA27">
-        <v>0.99783818599396734</v>
+        <v>0.9990379272460751</v>
       </c>
       <c r="AB27">
-        <v>39.633256777265125</v>
+        <v>17.638000488623998</v>
       </c>
       <c r="AD27" t="s">
         <v>249</v>
       </c>
       <c r="AE27" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AF27" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -8794,19 +8851,19 @@
         <v>176</v>
       </c>
       <c r="AL27" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AM27" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AN27" t="s">
-        <v>316</v>
+        <v>393</v>
       </c>
       <c r="AO27">
-        <v>0.99798114961534334</v>
+        <v>0.99841270356566336</v>
       </c>
       <c r="AP27">
-        <v>37.012257052039594</v>
+        <v>29.100434629504111</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8838,10 +8895,10 @@
         <v>242</v>
       </c>
       <c r="L28">
-        <v>23.3954191787236</v>
+        <v>21.708919178723601</v>
       </c>
       <c r="M28">
-        <v>0.14124198799860169</v>
+        <v>0.14131508612803251</v>
       </c>
       <c r="O28" t="s">
         <v>249</v>
@@ -8871,25 +8928,25 @@
         <v>286</v>
       </c>
       <c r="Y28" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA28">
-        <v>0.9966615805732193</v>
+        <v>0.99799850025928361</v>
       </c>
       <c r="AB28">
-        <v>61.204356157646131</v>
+        <v>36.694161913134486</v>
       </c>
       <c r="AD28" t="s">
         <v>249</v>
       </c>
       <c r="AE28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AF28" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -8904,19 +8961,19 @@
         <v>176</v>
       </c>
       <c r="AL28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AM28" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="AN28" t="s">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="AO28">
-        <v>0.99664078053750105</v>
+        <v>0.99851346011788389</v>
       </c>
       <c r="AP28">
-        <v>61.585690145814638</v>
+        <v>27.253231172129635</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8948,10 +9005,10 @@
         <v>243</v>
       </c>
       <c r="L29">
-        <v>20.01197763203729</v>
+        <v>19.406077632037299</v>
       </c>
       <c r="M29">
-        <v>0.13366475380241499</v>
+        <v>0.1336442556313891</v>
       </c>
       <c r="O29" t="s">
         <v>249</v>
@@ -8981,25 +9038,25 @@
         <v>288</v>
       </c>
       <c r="Y29" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Z29" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AA29">
-        <v>0.99852845242200794</v>
+        <v>0.99825653144816662</v>
       </c>
       <c r="AB29">
-        <v>26.978372263188255</v>
+        <v>31.963590116946214</v>
       </c>
       <c r="AD29" t="s">
         <v>249</v>
       </c>
       <c r="AE29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AF29" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -9014,19 +9071,19 @@
         <v>176</v>
       </c>
       <c r="AL29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AM29" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AN29" t="s">
-        <v>307</v>
+        <v>397</v>
       </c>
       <c r="AO29">
-        <v>0.99851437709898627</v>
+        <v>0.99889044265692783</v>
       </c>
       <c r="AP29">
-        <v>27.236419851917539</v>
+        <v>20.341884622989713</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9058,10 +9115,10 @@
         <v>244</v>
       </c>
       <c r="L30">
-        <v>23.591873553963495</v>
+        <v>22.919873553963495</v>
       </c>
       <c r="M30">
-        <v>0.13360401365368399</v>
+        <v>0.13357684214788279</v>
       </c>
       <c r="O30" t="s">
         <v>249</v>
@@ -9091,25 +9148,25 @@
         <v>290</v>
       </c>
       <c r="Y30" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="Z30" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AA30">
-        <v>0.9982564657516575</v>
+        <v>0.99838020422910712</v>
       </c>
       <c r="AB30">
-        <v>31.964794552945094</v>
+        <v>29.696255799702563</v>
       </c>
       <c r="AD30" t="s">
         <v>249</v>
       </c>
       <c r="AE30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AF30" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -9124,19 +9181,19 @@
         <v>176</v>
       </c>
       <c r="AL30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AM30" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AN30" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AO30">
-        <v>0.9985540071847413</v>
+        <v>0.99826829694347163</v>
       </c>
       <c r="AP30">
-        <v>26.509868279743756</v>
+        <v>31.747889369687481</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9168,10 +9225,10 @@
         <v>245</v>
       </c>
       <c r="L31">
-        <v>21.653826323424543</v>
+        <v>21.453026323424542</v>
       </c>
       <c r="M31">
-        <v>0.1321576257262759</v>
+        <v>0.1321554229544985</v>
       </c>
       <c r="O31" t="s">
         <v>249</v>
@@ -9201,25 +9258,25 @@
         <v>292</v>
       </c>
       <c r="Y31" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Z31" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AA31">
-        <v>0.99876909403276848</v>
+        <v>0.999066087582832</v>
       </c>
       <c r="AB31">
-        <v>22.56660939924376</v>
+        <v>17.121727648079396</v>
       </c>
       <c r="AD31" t="s">
         <v>249</v>
       </c>
       <c r="AE31" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AF31" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AG31" t="s">
         <v>10</v>
@@ -9234,19 +9291,19 @@
         <v>176</v>
       </c>
       <c r="AL31" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM31" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="AN31" t="s">
-        <v>393</v>
+        <v>302</v>
       </c>
       <c r="AO31">
-        <v>0.99831023082457615</v>
+        <v>0.99821490046920303</v>
       </c>
       <c r="AP31">
-        <v>30.979101549436738</v>
+        <v>32.726824731278626</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9278,10 +9335,10 @@
         <v>246</v>
       </c>
       <c r="L32">
-        <v>12.637613221312568</v>
+        <v>12.481913221312569</v>
       </c>
       <c r="M32">
-        <v>0.13378598692581661</v>
+        <v>0.13378469056061471</v>
       </c>
       <c r="O32" t="s">
         <v>249</v>
@@ -9311,25 +9368,25 @@
         <v>294</v>
       </c>
       <c r="Y32" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Z32" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AA32">
-        <v>0.9984521235218653</v>
+        <v>0.99819067543952888</v>
       </c>
       <c r="AB32">
-        <v>28.377735432469407</v>
+        <v>33.170950275304214</v>
       </c>
       <c r="AD32" t="s">
         <v>249</v>
       </c>
       <c r="AE32" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AF32" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG32" t="s">
         <v>10</v>
@@ -9344,19 +9401,19 @@
         <v>176</v>
       </c>
       <c r="AL32" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AM32" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AN32" t="s">
-        <v>308</v>
+        <v>402</v>
       </c>
       <c r="AO32">
-        <v>0.99785502426144801</v>
+        <v>0.9978557782095181</v>
       </c>
       <c r="AP32">
-        <v>39.324555206787501</v>
+        <v>39.310732825502484</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9388,10 +9445,10 @@
         <v>247</v>
       </c>
       <c r="L33">
-        <v>23.28078369016097</v>
+        <v>22.820883690160976</v>
       </c>
       <c r="M33">
-        <v>0.1336296330519684</v>
+        <v>0.13362377846039669</v>
       </c>
       <c r="O33" t="s">
         <v>249</v>
@@ -9421,16 +9478,16 @@
         <v>296</v>
       </c>
       <c r="Y33" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="Z33" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AA33">
-        <v>0.99831420288554851</v>
+        <v>0.99667108783610614</v>
       </c>
       <c r="AB33">
-        <v>30.906280431611009</v>
+        <v>61.030056338054941</v>
       </c>
     </row>
   </sheetData>
@@ -9439,7 +9496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B897863F-5FAA-4D4D-A4CC-C43A007D4C56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB57676D-4D45-4503-8054-A8B2CC256B50}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9530,10 +9587,10 @@
         <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D11" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9548,25 +9605,25 @@
         <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="K11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="L11">
-        <v>79.362778177778793</v>
+        <v>74.28777817777879</v>
       </c>
       <c r="M11">
-        <v>0.3211355802385743</v>
+        <v>0.32093648565823479</v>
       </c>
       <c r="O11" t="s">
         <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="Q11" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9581,16 +9638,16 @@
         <v>176</v>
       </c>
       <c r="W11" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="X11" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="Y11">
-        <v>108.8275</v>
+        <v>105.8785</v>
       </c>
       <c r="Z11">
-        <v>0.5723991316469299</v>
+        <v>0.57242635043266243</v>
       </c>
     </row>
     <row r="12" spans="2:26">
@@ -9598,10 +9655,10 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D12" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9616,25 +9673,25 @@
         <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="K12" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="L12">
-        <v>50.354564381123943</v>
+        <v>48.763564381123942</v>
       </c>
       <c r="M12">
-        <v>0.26229547975508177</v>
+        <v>0.26211330244569431</v>
       </c>
       <c r="O12" t="s">
         <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="Q12" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9649,16 +9706,16 @@
         <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="X12" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="Y12">
-        <v>54.292499999999997</v>
+        <v>53.662500000000001</v>
       </c>
       <c r="Z12">
-        <v>0.54240024081939597</v>
+        <v>0.54223332432757909</v>
       </c>
     </row>
     <row r="13" spans="2:26">
@@ -9666,10 +9723,10 @@
         <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D13" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -9684,25 +9741,25 @@
         <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="K13" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="L13">
-        <v>57.005439523831519</v>
+        <v>53.942439523831517</v>
       </c>
       <c r="M13">
-        <v>0.2700868018916121</v>
+        <v>0.2690363727663645</v>
       </c>
       <c r="O13" t="s">
         <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="Q13" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -9717,16 +9774,16 @@
         <v>176</v>
       </c>
       <c r="W13" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="X13" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="Y13">
-        <v>50.356250000000003</v>
+        <v>45.923250000000003</v>
       </c>
       <c r="Z13">
-        <v>0.53901340841870993</v>
+        <v>0.53710817920132903</v>
       </c>
     </row>
     <row r="14" spans="2:26">
@@ -9734,10 +9791,10 @@
         <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="D14" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -9752,25 +9809,25 @@
         <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="K14" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="L14">
-        <v>19.895723562817633</v>
+        <v>14.949238288353047</v>
       </c>
       <c r="M14">
-        <v>0.41998320265799222</v>
+        <v>0.40341579879346828</v>
       </c>
       <c r="O14" t="s">
         <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="Q14" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -9785,16 +9842,16 @@
         <v>176</v>
       </c>
       <c r="W14" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="X14" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="Y14">
-        <v>9.5987500000000008</v>
+        <v>9.4877500000000001</v>
       </c>
       <c r="Z14">
-        <v>0.44411317641629539</v>
+        <v>0.44399754476135089</v>
       </c>
     </row>
     <row r="15" spans="2:26">
@@ -9802,10 +9859,10 @@
         <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D15" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -9820,25 +9877,25 @@
         <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="K15" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="L15">
-        <v>9.5699994650614961</v>
+        <v>8.6309994650614961</v>
       </c>
       <c r="M15">
-        <v>0.44653362479084918</v>
+        <v>0.44764694985072379</v>
       </c>
       <c r="O15" t="s">
         <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="Q15" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -9853,16 +9910,16 @@
         <v>176</v>
       </c>
       <c r="W15" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="X15" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="Y15">
-        <v>50.66</v>
+        <v>48.856999999999999</v>
       </c>
       <c r="Z15">
-        <v>0.47592028835921918</v>
+        <v>0.4746891546603394</v>
       </c>
     </row>
     <row r="16" spans="2:26">
@@ -9870,10 +9927,10 @@
         <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D16" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -9888,25 +9945,25 @@
         <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="K16" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L16">
-        <v>44.760252416795389</v>
+        <v>40.594252416795392</v>
       </c>
       <c r="M16">
-        <v>0.42821243594155839</v>
+        <v>0.42614089168300978</v>
       </c>
       <c r="O16" t="s">
         <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="Q16" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -9921,10 +9978,10 @@
         <v>176</v>
       </c>
       <c r="W16" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="X16" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="Y16">
         <v>5.0000000000000001E-3</v>
@@ -9938,10 +9995,10 @@
         <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D17" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -9956,25 +10013,25 @@
         <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="K17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L17">
-        <v>40.59880776523103</v>
+        <v>38.826307765231029</v>
       </c>
       <c r="M17">
-        <v>0.34199105064435292</v>
+        <v>0.3416233223209601</v>
       </c>
       <c r="O17" t="s">
         <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="Q17" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -9989,10 +10046,10 @@
         <v>176</v>
       </c>
       <c r="W17" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="X17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Y17">
         <v>0.92625000000000002</v>
@@ -10006,10 +10063,10 @@
         <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D18" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -10024,25 +10081,25 @@
         <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="K18" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="L18">
-        <v>71.045385513132985</v>
+        <v>67.903385513132989</v>
       </c>
       <c r="M18">
-        <v>0.30696999788148871</v>
+        <v>0.30622401943451838</v>
       </c>
       <c r="O18" t="s">
         <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="Q18" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -10057,10 +10114,10 @@
         <v>176</v>
       </c>
       <c r="W18" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="X18" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="Y18">
         <v>7.5287499999999996</v>
@@ -10074,10 +10131,10 @@
         <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="D19" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -10092,25 +10149,25 @@
         <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="K19" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="L19">
-        <v>63.055598832310729</v>
+        <v>58.356098832310728</v>
       </c>
       <c r="M19">
-        <v>0.3285833535058732</v>
+        <v>0.32879312968784791</v>
       </c>
       <c r="O19" t="s">
         <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="Q19" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -10125,7 +10182,7 @@
         <v>176</v>
       </c>
       <c r="W19" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="X19" t="s">
         <v>423</v>
@@ -10142,10 +10199,10 @@
         <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D20" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -10160,25 +10217,25 @@
         <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="K20" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="L20">
-        <v>43.89469200396065</v>
+        <v>41.561692003960651</v>
       </c>
       <c r="M20">
-        <v>0.28382217649005848</v>
+        <v>0.2839199523619475</v>
       </c>
       <c r="O20" t="s">
         <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="Q20" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -10193,10 +10250,10 @@
         <v>176</v>
       </c>
       <c r="W20" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="X20" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="Y20">
         <v>0.24374999999999999</v>
@@ -10210,10 +10267,10 @@
         <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="D21" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -10228,10 +10285,10 @@
         <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="K21" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="L21">
         <v>11.547936358898198</v>
@@ -10245,10 +10302,10 @@
         <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="D22" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -10263,16 +10320,16 @@
         <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="K22" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="L22">
-        <v>31.481356456094364</v>
+        <v>31.412356456094365</v>
       </c>
       <c r="M22">
-        <v>0.2069371426129745</v>
+        <v>0.20690068202208589</v>
       </c>
     </row>
     <row r="23" spans="2:26">
@@ -10280,10 +10337,10 @@
         <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D23" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -10298,16 +10355,16 @@
         <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="K23" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="L23">
-        <v>15.708789779919334</v>
+        <v>15.682789779919334</v>
       </c>
       <c r="M23">
-        <v>0.17539476230326029</v>
+        <v>0.1753805450223308</v>
       </c>
     </row>
     <row r="24" spans="2:26">
@@ -10315,10 +10372,10 @@
         <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="D24" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -10333,10 +10390,10 @@
         <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="K24" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="L24">
         <v>20.814752751471318</v>
@@ -10350,10 +10407,10 @@
         <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="D25" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -10368,16 +10425,16 @@
         <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="K25" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="L25">
-        <v>50.266717026070005</v>
+        <v>48.290717026070006</v>
       </c>
       <c r="M25">
-        <v>0.24965463639883681</v>
+        <v>0.2491704659849456</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -10385,10 +10442,10 @@
         <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="D26" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -10403,16 +10460,16 @@
         <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="K26" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L26">
-        <v>56.728889145623882</v>
+        <v>55.472889145623881</v>
       </c>
       <c r="M26">
-        <v>0.22062927765182611</v>
+        <v>0.2205291811302611</v>
       </c>
     </row>
     <row r="27" spans="2:26">
@@ -10420,10 +10477,10 @@
         <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="D27" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -10438,16 +10495,16 @@
         <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="K27" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="L27">
-        <v>70.602917671125681</v>
+        <v>68.690917671125689</v>
       </c>
       <c r="M27">
-        <v>0.25064150011337971</v>
+        <v>0.25038498158950268</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -10455,10 +10512,10 @@
         <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D28" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -10473,16 +10530,16 @@
         <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="K28" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L28">
-        <v>7.8153674765988201</v>
+        <v>7.7433674765988201</v>
       </c>
       <c r="M28">
-        <v>0.1725941184630719</v>
+        <v>0.17252671423811</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -10490,10 +10547,10 @@
         <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="D29" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -10508,16 +10565,16 @@
         <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="K29" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="L29">
-        <v>26.861604762024118</v>
+        <v>26.55160476202412</v>
       </c>
       <c r="M29">
-        <v>0.19566496306844169</v>
+        <v>0.19548530634506781</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -10525,10 +10582,10 @@
         <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="D30" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -10543,10 +10600,10 @@
         <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="K30" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="L30">
         <v>10.889866530825216</v>
@@ -10560,10 +10617,10 @@
         <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="D31" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -10578,16 +10635,16 @@
         <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="K31" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L31">
-        <v>9.0084683548455349</v>
+        <v>8.9424683548455342</v>
       </c>
       <c r="M31">
-        <v>0.17747113378853541</v>
+        <v>0.1775141682488891</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -10595,10 +10652,10 @@
         <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="D32" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -10613,16 +10670,16 @@
         <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="K32" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="L32">
-        <v>35.009005865752776</v>
+        <v>34.831005865752779</v>
       </c>
       <c r="M32">
-        <v>0.1603815301266899</v>
+        <v>0.16034664831889561</v>
       </c>
     </row>
   </sheetData>
@@ -10631,19 +10688,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B8DC5F-3A61-4BEC-A2F4-ABBFAAC8054B}">
-  <dimension ref="B9:P73"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873FB49C-B3AE-4575-ACFE-70BFC46FF58A}">
+  <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:19">
       <c r="B9" t="s">
         <v>221</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:19">
       <c r="B10" t="s">
         <v>166</v>
       </c>
@@ -10654,452 +10711,479 @@
         <v>222</v>
       </c>
       <c r="E10">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F10">
         <v>2030</v>
       </c>
       <c r="G10">
+        <v>2035</v>
+      </c>
+      <c r="H10">
+        <v>2040</v>
+      </c>
+      <c r="I10">
+        <v>2045</v>
+      </c>
+      <c r="J10">
         <v>2050</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
         <v>54</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>165</v>
       </c>
-      <c r="K10" t="s">
+      <c r="N10" t="s">
         <v>166</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O10" t="s">
         <v>167</v>
       </c>
-      <c r="M10" t="s">
+      <c r="P10" t="s">
         <v>168</v>
       </c>
-      <c r="N10" t="s">
+      <c r="Q10" t="s">
         <v>169</v>
       </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
         <v>170</v>
       </c>
-      <c r="P10" t="s">
+      <c r="S10" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:19">
       <c r="B11" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11">
-        <v>0.30000000000000004</v>
+        <v>1000</v>
       </c>
       <c r="F11">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="G11">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="H11" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>503</v>
+      </c>
+      <c r="M11" t="s">
         <v>172</v>
       </c>
-      <c r="K11" t="s">
-        <v>491</v>
-      </c>
-      <c r="M11" t="s">
-        <v>10</v>
-      </c>
       <c r="N11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" t="s">
+        <v>502</v>
+      </c>
+      <c r="P11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
         <v>253</v>
       </c>
-      <c r="P11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16">
+      <c r="S11" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
       <c r="B12" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0.60000000000000009</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G12">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="H12" t="s">
-        <v>492</v>
-      </c>
-      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>504</v>
+      </c>
+      <c r="M12" t="s">
         <v>172</v>
       </c>
-      <c r="K12" t="s">
-        <v>496</v>
-      </c>
-      <c r="M12" t="s">
-        <v>10</v>
-      </c>
       <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
+        <v>508</v>
+      </c>
+      <c r="P12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
         <v>253</v>
       </c>
-      <c r="P12" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16">
+      <c r="S12" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
       <c r="B13" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
       </c>
       <c r="E13">
-        <v>5750</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="F13">
-        <v>5700</v>
-      </c>
-      <c r="G13">
-        <v>5100</v>
-      </c>
-      <c r="H13" t="s">
-        <v>493</v>
-      </c>
-      <c r="J13" t="s">
-        <v>172</v>
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="J13">
+        <v>0.497</v>
       </c>
       <c r="K13" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="M13" t="s">
-        <v>10</v>
+        <v>531</v>
       </c>
       <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
+        <v>509</v>
+      </c>
+      <c r="P13" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
         <v>253</v>
       </c>
-      <c r="P13" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16">
+      <c r="S13" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19">
       <c r="B14" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14">
-        <v>200</v>
+        <v>0.59</v>
       </c>
       <c r="F14">
-        <v>200</v>
-      </c>
-      <c r="G14">
-        <v>175</v>
-      </c>
-      <c r="H14" t="s">
-        <v>494</v>
-      </c>
-      <c r="J14" t="s">
+        <v>0.6</v>
+      </c>
+      <c r="J14">
+        <v>0.61</v>
+      </c>
+      <c r="K14" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" t="s">
         <v>172</v>
       </c>
-      <c r="K14" t="s">
-        <v>498</v>
-      </c>
-      <c r="M14" t="s">
-        <v>10</v>
-      </c>
       <c r="N14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
+        <v>512</v>
+      </c>
+      <c r="P14" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
         <v>253</v>
       </c>
-      <c r="P14" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16">
+      <c r="S14" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
       <c r="B15" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15" t="s">
-        <v>495</v>
-      </c>
-      <c r="J15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>30</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>30</v>
+      </c>
+      <c r="K15" t="s">
+        <v>506</v>
+      </c>
+      <c r="M15" t="s">
         <v>172</v>
       </c>
-      <c r="K15" t="s">
-        <v>499</v>
-      </c>
-      <c r="M15" t="s">
-        <v>10</v>
-      </c>
       <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
+        <v>513</v>
+      </c>
+      <c r="P15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
         <v>253</v>
       </c>
-      <c r="P15" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16">
+      <c r="S15" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
       <c r="B16" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16">
-        <v>0.35000000000000003</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>0.35000000000000003</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H16" t="s">
-        <v>146</v>
-      </c>
-      <c r="J16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>507</v>
+      </c>
+      <c r="M16" t="s">
         <v>172</v>
       </c>
-      <c r="K16" t="s">
-        <v>500</v>
-      </c>
-      <c r="M16" t="s">
-        <v>10</v>
-      </c>
       <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
+        <v>515</v>
+      </c>
+      <c r="P16" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
         <v>253</v>
       </c>
-      <c r="P16" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16">
+      <c r="S16" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17">
-        <v>0.60000000000000009</v>
+        <v>500</v>
       </c>
       <c r="F17">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G17">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="H17" t="s">
-        <v>492</v>
-      </c>
-      <c r="J17" t="s">
+        <v>500</v>
+      </c>
+      <c r="J17">
+        <v>500</v>
+      </c>
+      <c r="K17" t="s">
+        <v>503</v>
+      </c>
+      <c r="M17" t="s">
         <v>172</v>
       </c>
-      <c r="K17" t="s">
-        <v>501</v>
-      </c>
-      <c r="M17" t="s">
-        <v>10</v>
-      </c>
       <c r="N17" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" t="s">
+        <v>516</v>
+      </c>
+      <c r="P17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
         <v>253</v>
       </c>
-      <c r="P17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16">
+      <c r="S17" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
       <c r="B18" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
       </c>
       <c r="E18">
-        <v>2400</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>2350</v>
-      </c>
-      <c r="G18">
-        <v>2300</v>
-      </c>
-      <c r="H18" t="s">
-        <v>493</v>
-      </c>
-      <c r="J18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18" t="s">
+        <v>504</v>
+      </c>
+      <c r="M18" t="s">
         <v>172</v>
       </c>
-      <c r="K18" t="s">
-        <v>502</v>
-      </c>
-      <c r="M18" t="s">
-        <v>10</v>
-      </c>
       <c r="N18" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" t="s">
+        <v>517</v>
+      </c>
+      <c r="P18" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" t="s">
         <v>253</v>
       </c>
-      <c r="P18" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16">
+      <c r="S18" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
       <c r="B19" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
       </c>
       <c r="E19">
-        <v>85</v>
+        <v>1.9279999999999999</v>
       </c>
       <c r="F19">
-        <v>85</v>
-      </c>
-      <c r="G19">
-        <v>80</v>
-      </c>
-      <c r="H19" t="s">
-        <v>494</v>
-      </c>
-      <c r="J19" t="s">
+        <v>1.9279999999999999</v>
+      </c>
+      <c r="J19">
+        <v>1.9279999999999999</v>
+      </c>
+      <c r="K19" t="s">
+        <v>505</v>
+      </c>
+      <c r="M19" t="s">
         <v>172</v>
       </c>
-      <c r="K19" t="s">
-        <v>503</v>
-      </c>
-      <c r="M19" t="s">
-        <v>10</v>
-      </c>
       <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
+        <v>518</v>
+      </c>
+      <c r="P19" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
         <v>253</v>
       </c>
-      <c r="P19" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16">
+      <c r="S19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>495</v>
-      </c>
-      <c r="J20" t="s">
+        <v>0.41</v>
+      </c>
+      <c r="J20">
+        <v>0.42</v>
+      </c>
+      <c r="K20" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" t="s">
         <v>172</v>
       </c>
-      <c r="K20" t="s">
-        <v>504</v>
-      </c>
-      <c r="M20" t="s">
-        <v>10</v>
-      </c>
       <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
+        <v>519</v>
+      </c>
+      <c r="P20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
         <v>253</v>
       </c>
-      <c r="P20" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16">
+      <c r="S20" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -11108,39 +11192,48 @@
         <v>19</v>
       </c>
       <c r="E21">
-        <v>0.59</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>0.6</v>
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>0.61</v>
-      </c>
-      <c r="H21" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>30</v>
+      </c>
+      <c r="I21">
+        <v>30</v>
+      </c>
+      <c r="J21">
+        <v>30</v>
+      </c>
+      <c r="K21" t="s">
+        <v>506</v>
+      </c>
+      <c r="M21" t="s">
         <v>172</v>
       </c>
-      <c r="K21" t="s">
-        <v>505</v>
-      </c>
-      <c r="M21" t="s">
-        <v>10</v>
-      </c>
       <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
+        <v>520</v>
+      </c>
+      <c r="P21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
         <v>253</v>
       </c>
-      <c r="P21" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16">
+      <c r="S21" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -11149,290 +11242,362 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1000</v>
-      </c>
-      <c r="H22" t="s">
-        <v>493</v>
-      </c>
-      <c r="J22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>507</v>
+      </c>
+      <c r="M22" t="s">
         <v>172</v>
       </c>
-      <c r="K22" t="s">
-        <v>506</v>
-      </c>
-      <c r="M22" t="s">
-        <v>10</v>
-      </c>
       <c r="N22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" t="s">
+        <v>521</v>
+      </c>
+      <c r="P22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
         <v>253</v>
       </c>
-      <c r="P22" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16">
+      <c r="S22" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>1300</v>
       </c>
       <c r="F23">
-        <v>25</v>
-      </c>
-      <c r="G23">
-        <v>25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>494</v>
-      </c>
-      <c r="J23" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J23">
+        <v>1300</v>
+      </c>
+      <c r="K23" t="s">
+        <v>503</v>
+      </c>
+      <c r="M23" t="s">
         <v>172</v>
       </c>
-      <c r="K23" t="s">
-        <v>507</v>
-      </c>
-      <c r="M23" t="s">
-        <v>10</v>
-      </c>
       <c r="N23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" t="s">
+        <v>522</v>
+      </c>
+      <c r="P23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
         <v>253</v>
       </c>
-      <c r="P23" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16">
+      <c r="S23" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
       <c r="B24" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="E24">
-        <v>0.51</v>
+        <v>40</v>
       </c>
       <c r="F24">
-        <v>0.52</v>
-      </c>
-      <c r="G24">
-        <v>0.54</v>
-      </c>
-      <c r="H24" t="s">
-        <v>146</v>
-      </c>
-      <c r="J24" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24">
+        <v>40</v>
+      </c>
+      <c r="K24" t="s">
+        <v>504</v>
+      </c>
+      <c r="M24" t="s">
         <v>172</v>
       </c>
-      <c r="K24" t="s">
-        <v>508</v>
-      </c>
-      <c r="M24" t="s">
-        <v>10</v>
-      </c>
       <c r="N24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" t="s">
+        <v>523</v>
+      </c>
+      <c r="P24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
         <v>253</v>
       </c>
-      <c r="P24" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16">
+      <c r="S24" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
       <c r="B25" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="E25">
-        <v>3100</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="F25">
-        <v>3100</v>
-      </c>
-      <c r="G25">
-        <v>2400</v>
-      </c>
-      <c r="H25" t="s">
-        <v>493</v>
-      </c>
-      <c r="J25" t="s">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="J25">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="K25" t="s">
+        <v>505</v>
+      </c>
+      <c r="M25" t="s">
         <v>172</v>
       </c>
-      <c r="K25" t="s">
+      <c r="N25" t="s">
+        <v>524</v>
+      </c>
+      <c r="P25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
+        <v>253</v>
+      </c>
+      <c r="S25" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" t="s">
         <v>509</v>
-      </c>
-      <c r="M25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
-        <v>253</v>
-      </c>
-      <c r="P25" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16">
-      <c r="B26" t="s">
-        <v>498</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="E26">
-        <v>75</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="F26">
-        <v>75</v>
-      </c>
-      <c r="G26">
-        <v>60</v>
-      </c>
-      <c r="H26" t="s">
-        <v>494</v>
-      </c>
-      <c r="J26" t="s">
+        <v>0.54</v>
+      </c>
+      <c r="J26">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="K26" t="s">
+        <v>146</v>
+      </c>
+      <c r="M26" t="s">
         <v>172</v>
       </c>
-      <c r="K26" t="s">
+      <c r="N26" t="s">
+        <v>526</v>
+      </c>
+      <c r="P26" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
+        <v>253</v>
+      </c>
+      <c r="S26" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" t="s">
+        <v>509</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
         <v>510</v>
       </c>
-      <c r="M26" t="s">
-        <v>10</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="E27">
+        <v>25</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>25</v>
+      </c>
+      <c r="J27">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>506</v>
+      </c>
+      <c r="M27" t="s">
+        <v>531</v>
+      </c>
+      <c r="N27" t="s">
+        <v>527</v>
+      </c>
+      <c r="P27" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
         <v>253</v>
       </c>
-      <c r="P26" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16">
-      <c r="B27" t="s">
-        <v>499</v>
-      </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27">
-        <v>0.37</v>
-      </c>
-      <c r="F27">
-        <v>0.38</v>
-      </c>
-      <c r="G27">
-        <v>0.39</v>
-      </c>
-      <c r="H27" t="s">
-        <v>146</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="S27" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="B28" t="s">
+        <v>509</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>510</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28" t="s">
+        <v>507</v>
+      </c>
+      <c r="M28" t="s">
         <v>172</v>
       </c>
-      <c r="K27" t="s">
+      <c r="N28" t="s">
+        <v>528</v>
+      </c>
+      <c r="P28" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" t="s">
+        <v>253</v>
+      </c>
+      <c r="S28" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19">
+      <c r="B29" t="s">
+        <v>509</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
+        <v>510</v>
+      </c>
+      <c r="E29">
+        <v>1.0952</v>
+      </c>
+      <c r="F29">
+        <v>1.0952</v>
+      </c>
+      <c r="G29">
+        <v>1.0952</v>
+      </c>
+      <c r="H29">
+        <v>1.0952</v>
+      </c>
+      <c r="I29">
+        <v>1.0952</v>
+      </c>
+      <c r="J29">
+        <v>1.0952</v>
+      </c>
+      <c r="K29" t="s">
+        <v>511</v>
+      </c>
+      <c r="M29" t="s">
+        <v>172</v>
+      </c>
+      <c r="N29" t="s">
+        <v>529</v>
+      </c>
+      <c r="P29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>253</v>
+      </c>
+      <c r="S29" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19">
+      <c r="B30" t="s">
         <v>512</v>
-      </c>
-      <c r="M27" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P27" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16">
-      <c r="B28" t="s">
-        <v>499</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28">
-        <v>5500</v>
-      </c>
-      <c r="F28">
-        <v>5500</v>
-      </c>
-      <c r="G28">
-        <v>4350</v>
-      </c>
-      <c r="H28" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16">
-      <c r="B29" t="s">
-        <v>499</v>
-      </c>
-      <c r="C29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29">
-        <v>165</v>
-      </c>
-      <c r="F29">
-        <v>165</v>
-      </c>
-      <c r="G29">
-        <v>130</v>
-      </c>
-      <c r="H29" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16">
-      <c r="B30" t="s">
-        <v>500</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -11441,21 +11606,21 @@
         <v>19</v>
       </c>
       <c r="E30">
-        <v>0.4</v>
+        <v>5000</v>
       </c>
       <c r="F30">
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="G30">
-        <v>0.42</v>
-      </c>
-      <c r="H30" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16">
+        <v>2500</v>
+      </c>
+      <c r="J30">
+        <v>2500</v>
+      </c>
+      <c r="K30" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19">
       <c r="B31" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -11464,21 +11629,21 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>500</v>
-      </c>
-      <c r="G31">
-        <v>500</v>
-      </c>
-      <c r="H31" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16">
+        <v>50</v>
+      </c>
+      <c r="J31">
+        <v>50</v>
+      </c>
+      <c r="K31" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19">
       <c r="B32" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -11487,228 +11652,264 @@
         <v>19</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="F32">
-        <v>20</v>
-      </c>
-      <c r="G32">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="J32">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="K32" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
       <c r="B33" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
+        <v>0.54</v>
+      </c>
+      <c r="J33">
+        <v>0.6</v>
+      </c>
+      <c r="K33" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:11">
       <c r="B34" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0.35000000000000003</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>0.35000000000000003</v>
+        <v>20</v>
       </c>
       <c r="G34">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H34" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>20</v>
+      </c>
+      <c r="I34">
+        <v>20</v>
+      </c>
+      <c r="J34">
+        <v>20</v>
+      </c>
+      <c r="K34" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
       <c r="B35" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
       </c>
       <c r="E35">
-        <v>2650</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>2650</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>2650</v>
-      </c>
-      <c r="H35" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
       <c r="B36" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="E36">
-        <v>65</v>
+        <v>3100</v>
       </c>
       <c r="F36">
-        <v>65</v>
-      </c>
-      <c r="G36">
-        <v>65</v>
-      </c>
-      <c r="H36" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
+        <v>3100</v>
+      </c>
+      <c r="J36">
+        <v>2500</v>
+      </c>
+      <c r="K36" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
       <c r="B37" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="F37">
-        <v>4</v>
-      </c>
-      <c r="G37">
-        <v>4</v>
-      </c>
-      <c r="H37" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
+        <v>75</v>
+      </c>
+      <c r="J37">
+        <v>60</v>
+      </c>
+      <c r="K37" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
       <c r="B38" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="E38">
-        <v>0.45</v>
+        <v>1.35</v>
       </c>
       <c r="F38">
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="G38">
-        <v>0.5</v>
-      </c>
-      <c r="H38" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
+        <v>1.2</v>
+      </c>
+      <c r="J38">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="K38" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
       <c r="B39" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="E39">
-        <v>2500</v>
+        <v>0.51</v>
       </c>
       <c r="F39">
-        <v>2350</v>
-      </c>
-      <c r="G39">
-        <v>2300</v>
-      </c>
-      <c r="H39" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
+        <v>0.52</v>
+      </c>
+      <c r="J39">
+        <v>0.52</v>
+      </c>
+      <c r="K39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
       <c r="B40" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="E40">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="G40">
-        <v>80</v>
-      </c>
-      <c r="H40" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
+        <v>30</v>
+      </c>
+      <c r="H40">
+        <v>30</v>
+      </c>
+      <c r="I40">
+        <v>30</v>
+      </c>
+      <c r="J40">
+        <v>30</v>
+      </c>
+      <c r="K40" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
       <c r="B41" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="C41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="E41">
-        <v>0.36</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>0.38</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>0.43</v>
-      </c>
-      <c r="H41" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
       <c r="B42" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -11717,21 +11918,21 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>5850</v>
+        <v>1700</v>
       </c>
       <c r="F42">
-        <v>5700</v>
-      </c>
-      <c r="G42">
-        <v>5100</v>
-      </c>
-      <c r="H42" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
+        <v>1700</v>
+      </c>
+      <c r="J42">
+        <v>1700</v>
+      </c>
+      <c r="K42" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
       <c r="B43" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -11740,90 +11941,99 @@
         <v>19</v>
       </c>
       <c r="E43">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="F43">
-        <v>200</v>
-      </c>
-      <c r="G43">
-        <v>180</v>
-      </c>
-      <c r="H43" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
+        <v>45</v>
+      </c>
+      <c r="J43">
+        <v>45</v>
+      </c>
+      <c r="K43" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
       <c r="B44" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
       </c>
       <c r="E44">
-        <v>0.33</v>
+        <v>2.3610000000000002</v>
       </c>
       <c r="F44">
-        <v>0.33</v>
-      </c>
-      <c r="G44">
-        <v>0.33</v>
-      </c>
-      <c r="H44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="J44">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="K44" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
       <c r="B45" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
       </c>
       <c r="E45">
-        <v>6600</v>
+        <v>0.39</v>
       </c>
       <c r="F45">
-        <v>5100</v>
-      </c>
-      <c r="G45">
-        <v>4500</v>
-      </c>
-      <c r="H45" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
+        <v>0.39</v>
+      </c>
+      <c r="J45">
+        <v>0.39</v>
+      </c>
+      <c r="K45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
       <c r="B46" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
       </c>
       <c r="E46">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="F46">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="G46">
-        <v>160</v>
-      </c>
-      <c r="H46" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H46">
+        <v>40</v>
+      </c>
+      <c r="I46">
+        <v>40</v>
+      </c>
+      <c r="J46">
+        <v>40</v>
+      </c>
+      <c r="K46" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
       <c r="B47" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -11832,21 +12042,30 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>0.37</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>0.38</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>0.39</v>
-      </c>
-      <c r="H47" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
       <c r="B48" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -11855,21 +12074,21 @@
         <v>19</v>
       </c>
       <c r="E48">
-        <v>5700</v>
+        <v>2000</v>
       </c>
       <c r="F48">
-        <v>5700</v>
-      </c>
-      <c r="G48">
-        <v>5100</v>
-      </c>
-      <c r="H48" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
+        <v>2000</v>
+      </c>
+      <c r="J48">
+        <v>2000</v>
+      </c>
+      <c r="K48" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
       <c r="B49" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -11878,136 +12097,154 @@
         <v>19</v>
       </c>
       <c r="E49">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="F49">
-        <v>170</v>
-      </c>
-      <c r="G49">
-        <v>155</v>
-      </c>
-      <c r="H49" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
+        <v>60</v>
+      </c>
+      <c r="J49">
+        <v>60</v>
+      </c>
+      <c r="K49" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
       <c r="B50" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
         <v>19</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2.5830000000000002</v>
       </c>
       <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
+        <v>2.4969999999999999</v>
+      </c>
+      <c r="J50">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="K50" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
       </c>
       <c r="E51">
-        <v>0.14000000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="F51">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G51">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H51" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
+        <v>0.43</v>
+      </c>
+      <c r="J51">
+        <v>0.43</v>
+      </c>
+      <c r="K51" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
       </c>
       <c r="E52">
-        <v>750</v>
+        <v>40</v>
       </c>
       <c r="F52">
-        <v>480</v>
+        <v>40</v>
       </c>
       <c r="G52">
-        <v>340</v>
-      </c>
-      <c r="H52" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H52">
+        <v>40</v>
+      </c>
+      <c r="I52">
+        <v>40</v>
+      </c>
+      <c r="J52">
+        <v>40</v>
+      </c>
+      <c r="K52" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
       </c>
       <c r="E53">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F53">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>10</v>
-      </c>
-      <c r="H53" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
+      <c r="K53" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
         <v>19</v>
       </c>
       <c r="E54">
-        <v>1.5</v>
+        <v>2200</v>
       </c>
       <c r="F54">
-        <v>1.5</v>
-      </c>
-      <c r="G54">
-        <v>1.5</v>
-      </c>
-      <c r="H54" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
+        <v>2200</v>
+      </c>
+      <c r="J54">
+        <v>2200</v>
+      </c>
+      <c r="K54" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -12016,21 +12253,21 @@
         <v>19</v>
       </c>
       <c r="E55">
-        <v>0.39</v>
+        <v>65</v>
       </c>
       <c r="F55">
-        <v>0.39</v>
-      </c>
-      <c r="G55">
-        <v>0.39</v>
-      </c>
-      <c r="H55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
+        <v>65</v>
+      </c>
+      <c r="J55">
+        <v>65</v>
+      </c>
+      <c r="K55" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -12039,21 +12276,21 @@
         <v>19</v>
       </c>
       <c r="E56">
-        <v>1700</v>
+        <v>2.6389999999999998</v>
       </c>
       <c r="F56">
-        <v>1700</v>
-      </c>
-      <c r="G56">
-        <v>1700</v>
-      </c>
-      <c r="H56" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="J56">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="K56" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -12062,21 +12299,21 @@
         <v>19</v>
       </c>
       <c r="E57">
-        <v>45</v>
+        <v>0.45</v>
       </c>
       <c r="F57">
-        <v>45</v>
-      </c>
-      <c r="G57">
-        <v>45</v>
-      </c>
-      <c r="H57" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
+        <v>0.47</v>
+      </c>
+      <c r="J57">
+        <v>0.47</v>
+      </c>
+      <c r="K57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -12085,21 +12322,30 @@
         <v>19</v>
       </c>
       <c r="E58">
-        <v>0.43</v>
+        <v>40</v>
       </c>
       <c r="F58">
-        <v>0.43</v>
+        <v>40</v>
       </c>
       <c r="G58">
-        <v>0.43</v>
-      </c>
-      <c r="H58" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H58">
+        <v>40</v>
+      </c>
+      <c r="I58">
+        <v>40</v>
+      </c>
+      <c r="J58">
+        <v>40</v>
+      </c>
+      <c r="K58" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -12108,21 +12354,30 @@
         <v>19</v>
       </c>
       <c r="E59">
-        <v>2000</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>2000</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>2000</v>
-      </c>
-      <c r="H59" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+      <c r="J59">
+        <v>4</v>
+      </c>
+      <c r="K59" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
       <c r="B60" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -12131,21 +12386,21 @@
         <v>19</v>
       </c>
       <c r="E60">
-        <v>60</v>
+        <v>2500</v>
       </c>
       <c r="F60">
-        <v>60</v>
-      </c>
-      <c r="G60">
-        <v>60</v>
-      </c>
-      <c r="H60" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
+        <v>2350</v>
+      </c>
+      <c r="J60">
+        <v>2300</v>
+      </c>
+      <c r="K60" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
       <c r="B61" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -12154,21 +12409,21 @@
         <v>19</v>
       </c>
       <c r="E61">
-        <v>0.46</v>
+        <v>95</v>
       </c>
       <c r="F61">
-        <v>0.46</v>
-      </c>
-      <c r="G61">
-        <v>0.48</v>
-      </c>
-      <c r="H61" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
+        <v>85</v>
+      </c>
+      <c r="J61">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
       <c r="B62" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -12177,21 +12432,21 @@
         <v>19</v>
       </c>
       <c r="E62">
-        <v>2200</v>
+        <v>0.44</v>
       </c>
       <c r="F62">
-        <v>2200</v>
-      </c>
-      <c r="G62">
-        <v>2200</v>
-      </c>
-      <c r="H62" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
+        <v>0.47</v>
+      </c>
+      <c r="J62">
+        <v>0.49</v>
+      </c>
+      <c r="K62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
       <c r="B63" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -12200,246 +12455,1733 @@
         <v>19</v>
       </c>
       <c r="E63">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F63">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="G63">
-        <v>65</v>
-      </c>
-      <c r="H63" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H63">
+        <v>40</v>
+      </c>
+      <c r="I63">
+        <v>40</v>
+      </c>
+      <c r="J63">
+        <v>40</v>
+      </c>
+      <c r="K63" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
       <c r="B64" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C64" t="s">
-        <v>511</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64">
+        <v>4</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" t="s">
+        <v>519</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" t="s">
+        <v>514</v>
+      </c>
+      <c r="E65">
+        <v>5500</v>
+      </c>
+      <c r="F65">
+        <v>5500</v>
+      </c>
+      <c r="J65">
+        <v>4500</v>
+      </c>
+      <c r="K65" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" t="s">
+        <v>519</v>
+      </c>
+      <c r="C66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" t="s">
+        <v>514</v>
+      </c>
+      <c r="E66">
+        <v>165</v>
+      </c>
+      <c r="F66">
+        <v>165</v>
+      </c>
+      <c r="J66">
+        <v>135</v>
+      </c>
+      <c r="K66" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" t="s">
+        <v>519</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" t="s">
+        <v>514</v>
+      </c>
+      <c r="E67">
+        <v>4.4779999999999998</v>
+      </c>
+      <c r="F67">
+        <v>4.1529999999999996</v>
+      </c>
+      <c r="J67">
+        <v>3.7309999999999999</v>
+      </c>
+      <c r="K67" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" t="s">
+        <v>519</v>
+      </c>
+      <c r="C68" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" t="s">
+        <v>514</v>
+      </c>
+      <c r="E68">
+        <v>0.36</v>
+      </c>
+      <c r="F68">
+        <v>0.37</v>
+      </c>
+      <c r="J68">
+        <v>0.37</v>
+      </c>
+      <c r="K68" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" t="s">
+    <row r="69" spans="2:11">
+      <c r="B69" t="s">
+        <v>519</v>
+      </c>
+      <c r="C69" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" t="s">
+        <v>514</v>
+      </c>
+      <c r="E69">
+        <v>40</v>
+      </c>
+      <c r="F69">
+        <v>40</v>
+      </c>
+      <c r="G69">
+        <v>40</v>
+      </c>
+      <c r="H69">
+        <v>40</v>
+      </c>
+      <c r="I69">
+        <v>40</v>
+      </c>
+      <c r="J69">
+        <v>40</v>
+      </c>
+      <c r="K69" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" t="s">
+        <v>519</v>
+      </c>
+      <c r="C70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" t="s">
+        <v>514</v>
+      </c>
+      <c r="E70">
+        <v>5</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
+      <c r="K70" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" t="s">
+        <v>520</v>
+      </c>
+      <c r="C71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" t="s">
+        <v>514</v>
+      </c>
+      <c r="E71">
+        <v>5850</v>
+      </c>
+      <c r="F71">
+        <v>5700</v>
+      </c>
+      <c r="J71">
+        <v>5150</v>
+      </c>
+      <c r="K71" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" t="s">
+        <v>520</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" t="s">
+        <v>514</v>
+      </c>
+      <c r="E72">
+        <v>205</v>
+      </c>
+      <c r="F72">
+        <v>200</v>
+      </c>
+      <c r="J72">
+        <v>180</v>
+      </c>
+      <c r="K72" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" t="s">
+        <v>520</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>514</v>
+      </c>
+      <c r="E73">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="F73">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="J73">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="K73" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" t="s">
+        <v>520</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
+        <v>514</v>
+      </c>
+      <c r="E74">
+        <v>0.35</v>
+      </c>
+      <c r="F74">
+        <v>0.36</v>
+      </c>
+      <c r="J74">
+        <v>0.39</v>
+      </c>
+      <c r="K74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" t="s">
+        <v>520</v>
+      </c>
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" t="s">
+        <v>514</v>
+      </c>
+      <c r="E75">
+        <v>40</v>
+      </c>
+      <c r="F75">
+        <v>40</v>
+      </c>
+      <c r="G75">
+        <v>40</v>
+      </c>
+      <c r="H75">
+        <v>40</v>
+      </c>
+      <c r="I75">
+        <v>40</v>
+      </c>
+      <c r="J75">
+        <v>40</v>
+      </c>
+      <c r="K75" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" t="s">
+        <v>520</v>
+      </c>
+      <c r="C76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" t="s">
+        <v>514</v>
+      </c>
+      <c r="E76">
+        <v>5</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+      <c r="H76">
+        <v>5</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" t="s">
+        <v>521</v>
+      </c>
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" t="s">
+        <v>514</v>
+      </c>
+      <c r="E77">
+        <v>5700</v>
+      </c>
+      <c r="F77">
+        <v>5700</v>
+      </c>
+      <c r="J77">
+        <v>5150</v>
+      </c>
+      <c r="K77" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" t="s">
+        <v>521</v>
+      </c>
+      <c r="C78" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" t="s">
+        <v>514</v>
+      </c>
+      <c r="E78">
+        <v>170</v>
+      </c>
+      <c r="F78">
+        <v>170</v>
+      </c>
+      <c r="J78">
+        <v>155</v>
+      </c>
+      <c r="K78" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" t="s">
+        <v>521</v>
+      </c>
+      <c r="C79" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" t="s">
+        <v>514</v>
+      </c>
+      <c r="E79">
+        <v>4.306</v>
+      </c>
+      <c r="F79">
+        <v>4.306</v>
+      </c>
+      <c r="J79">
+        <v>4.306</v>
+      </c>
+      <c r="K79" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" t="s">
+        <v>521</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" t="s">
+        <v>514</v>
+      </c>
+      <c r="E80">
+        <v>0.36</v>
+      </c>
+      <c r="F80">
+        <v>0.37</v>
+      </c>
+      <c r="J80">
+        <v>0.37</v>
+      </c>
+      <c r="K80" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" t="s">
+        <v>521</v>
+      </c>
+      <c r="C81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" t="s">
+        <v>514</v>
+      </c>
+      <c r="E81">
+        <v>40</v>
+      </c>
+      <c r="F81">
+        <v>40</v>
+      </c>
+      <c r="G81">
+        <v>40</v>
+      </c>
+      <c r="H81">
+        <v>40</v>
+      </c>
+      <c r="I81">
+        <v>40</v>
+      </c>
+      <c r="J81">
+        <v>40</v>
+      </c>
+      <c r="K81" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" t="s">
+        <v>521</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>514</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82">
+        <v>5</v>
+      </c>
+      <c r="G82">
+        <v>5</v>
+      </c>
+      <c r="H82">
+        <v>5</v>
+      </c>
+      <c r="I82">
+        <v>5</v>
+      </c>
+      <c r="J82">
+        <v>5</v>
+      </c>
+      <c r="K82" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" t="s">
+        <v>522</v>
+      </c>
+      <c r="C83" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83">
+        <v>6600</v>
+      </c>
+      <c r="F83">
+        <v>5100</v>
+      </c>
+      <c r="J83">
+        <v>4500</v>
+      </c>
+      <c r="K83" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" t="s">
+        <v>522</v>
+      </c>
+      <c r="C84" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84">
+        <v>160</v>
+      </c>
+      <c r="F84">
+        <v>160</v>
+      </c>
+      <c r="J84">
+        <v>160</v>
+      </c>
+      <c r="K84" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" t="s">
+        <v>522</v>
+      </c>
+      <c r="C85" t="s">
+        <v>36</v>
+      </c>
+      <c r="D85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="J85">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="K85" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" t="s">
+        <v>522</v>
+      </c>
+      <c r="C86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D86" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86">
+        <v>60</v>
+      </c>
+      <c r="F86">
+        <v>60</v>
+      </c>
+      <c r="G86">
+        <v>60</v>
+      </c>
+      <c r="H86">
+        <v>60</v>
+      </c>
+      <c r="I86">
+        <v>60</v>
+      </c>
+      <c r="J86">
+        <v>60</v>
+      </c>
+      <c r="K86" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" t="s">
+        <v>522</v>
+      </c>
+      <c r="C87" t="s">
+        <v>36</v>
+      </c>
+      <c r="D87" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87">
+        <v>7</v>
+      </c>
+      <c r="F87">
+        <v>7</v>
+      </c>
+      <c r="G87">
+        <v>7</v>
+      </c>
+      <c r="H87">
+        <v>7</v>
+      </c>
+      <c r="I87">
+        <v>7</v>
+      </c>
+      <c r="J87">
+        <v>7</v>
+      </c>
+      <c r="K87" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" t="s">
+        <v>523</v>
+      </c>
+      <c r="C88" t="s">
+        <v>36</v>
+      </c>
+      <c r="D88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88">
+        <v>10253.1</v>
+      </c>
+      <c r="G88">
+        <v>7863</v>
+      </c>
+      <c r="H88">
+        <v>6373.8</v>
+      </c>
+      <c r="I88">
+        <v>5480.2</v>
+      </c>
+      <c r="J88">
+        <v>4884.6000000000004</v>
+      </c>
+      <c r="K88" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" t="s">
+        <v>523</v>
+      </c>
+      <c r="C89" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89">
+        <v>144.5</v>
+      </c>
+      <c r="G89">
+        <v>136</v>
+      </c>
+      <c r="H89">
+        <v>136</v>
+      </c>
+      <c r="I89">
+        <v>136</v>
+      </c>
+      <c r="J89">
+        <v>136</v>
+      </c>
+      <c r="K89" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" t="s">
+        <v>523</v>
+      </c>
+      <c r="C90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="G90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="H90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="I90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="J90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="K90" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" t="s">
+        <v>523</v>
+      </c>
+      <c r="C91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D91" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91">
+        <v>40</v>
+      </c>
+      <c r="F91">
+        <v>40</v>
+      </c>
+      <c r="G91">
+        <v>40</v>
+      </c>
+      <c r="H91">
+        <v>40</v>
+      </c>
+      <c r="I91">
+        <v>40</v>
+      </c>
+      <c r="J91">
+        <v>40</v>
+      </c>
+      <c r="K91" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" t="s">
+        <v>523</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <v>3</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92">
+        <v>3</v>
+      </c>
+      <c r="K92" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" t="s">
+        <v>524</v>
+      </c>
+      <c r="C93" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93">
+        <v>2400</v>
+      </c>
+      <c r="F93">
+        <v>2350</v>
+      </c>
+      <c r="J93">
+        <v>2300</v>
+      </c>
+      <c r="K93" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" t="s">
+        <v>524</v>
+      </c>
+      <c r="C94" t="s">
+        <v>31</v>
+      </c>
+      <c r="D94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94">
+        <v>85</v>
+      </c>
+      <c r="F94">
+        <v>80</v>
+      </c>
+      <c r="J94">
+        <v>80</v>
+      </c>
+      <c r="K94" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" t="s">
+        <v>524</v>
+      </c>
+      <c r="C95" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="F95">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="J95">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" t="s">
+        <v>524</v>
+      </c>
+      <c r="C96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96">
+        <v>0.35</v>
+      </c>
+      <c r="F96">
+        <v>0.35</v>
+      </c>
+      <c r="J96">
+        <v>0.35</v>
+      </c>
+      <c r="K96" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" t="s">
+        <v>524</v>
+      </c>
+      <c r="C97" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97">
+        <v>0.6</v>
+      </c>
+      <c r="F97">
+        <v>0.6</v>
+      </c>
+      <c r="J97">
+        <v>0.6</v>
+      </c>
+      <c r="K97" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" t="s">
+        <v>524</v>
+      </c>
+      <c r="C98" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98">
+        <v>45</v>
+      </c>
+      <c r="F98">
+        <v>45</v>
+      </c>
+      <c r="G98">
+        <v>45</v>
+      </c>
+      <c r="H98">
+        <v>45</v>
+      </c>
+      <c r="I98">
+        <v>45</v>
+      </c>
+      <c r="J98">
+        <v>45</v>
+      </c>
+      <c r="K98" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" t="s">
+        <v>524</v>
+      </c>
+      <c r="C99" t="s">
+        <v>31</v>
+      </c>
+      <c r="D99" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99">
+        <v>3</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99">
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99">
+        <v>3</v>
+      </c>
+      <c r="K99" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="B100" t="s">
+        <v>526</v>
+      </c>
+      <c r="C100" t="s">
+        <v>31</v>
+      </c>
+      <c r="D100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100">
+        <v>600</v>
+      </c>
+      <c r="F100">
+        <v>575</v>
+      </c>
+      <c r="J100">
+        <v>575</v>
+      </c>
+      <c r="K100" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" t="s">
+        <v>526</v>
+      </c>
+      <c r="C101" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101">
+        <v>25</v>
+      </c>
+      <c r="F101">
+        <v>20</v>
+      </c>
+      <c r="J101">
+        <v>20</v>
+      </c>
+      <c r="K101" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" t="s">
+        <v>526</v>
+      </c>
+      <c r="C102" t="s">
+        <v>31</v>
+      </c>
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102">
+        <v>1.111</v>
+      </c>
+      <c r="F102">
+        <v>1.111</v>
+      </c>
+      <c r="J102">
+        <v>1.111</v>
+      </c>
+      <c r="K102" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" t="s">
+        <v>526</v>
+      </c>
+      <c r="C103" t="s">
+        <v>31</v>
+      </c>
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103">
+        <v>0.37</v>
+      </c>
+      <c r="F103">
+        <v>0.37</v>
+      </c>
+      <c r="J103">
+        <v>0.37</v>
+      </c>
+      <c r="K103" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" t="s">
+        <v>526</v>
+      </c>
+      <c r="C104" t="s">
+        <v>31</v>
+      </c>
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104">
+        <v>0.6</v>
+      </c>
+      <c r="F104">
+        <v>0.6</v>
+      </c>
+      <c r="J104">
+        <v>0.6</v>
+      </c>
+      <c r="K104" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="B105" t="s">
+        <v>526</v>
+      </c>
+      <c r="C105" t="s">
+        <v>31</v>
+      </c>
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105">
+        <v>40</v>
+      </c>
+      <c r="F105">
+        <v>40</v>
+      </c>
+      <c r="G105">
+        <v>40</v>
+      </c>
+      <c r="H105">
+        <v>40</v>
+      </c>
+      <c r="I105">
+        <v>40</v>
+      </c>
+      <c r="J105">
+        <v>40</v>
+      </c>
+      <c r="K105" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" t="s">
+        <v>526</v>
+      </c>
+      <c r="C106" t="s">
+        <v>31</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>2</v>
+      </c>
+      <c r="H106">
+        <v>2</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="K106" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107" t="s">
+        <v>527</v>
+      </c>
+      <c r="C107" t="s">
+        <v>31</v>
+      </c>
+      <c r="D107" t="s">
         <v>510</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E107">
+        <v>3750</v>
+      </c>
+      <c r="F107">
+        <v>3650</v>
+      </c>
+      <c r="J107">
+        <v>3550</v>
+      </c>
+      <c r="K107" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="B108" t="s">
+        <v>527</v>
+      </c>
+      <c r="C108" t="s">
+        <v>31</v>
+      </c>
+      <c r="D108" t="s">
+        <v>510</v>
+      </c>
+      <c r="E108">
+        <v>140</v>
+      </c>
+      <c r="F108">
+        <v>140</v>
+      </c>
+      <c r="J108">
+        <v>130</v>
+      </c>
+      <c r="K108" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="B109" t="s">
+        <v>527</v>
+      </c>
+      <c r="C109" t="s">
+        <v>31</v>
+      </c>
+      <c r="D109" t="s">
+        <v>510</v>
+      </c>
+      <c r="E109">
+        <v>1.667</v>
+      </c>
+      <c r="F109">
+        <v>1.667</v>
+      </c>
+      <c r="J109">
+        <v>1.667</v>
+      </c>
+      <c r="K109" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="B110" t="s">
+        <v>527</v>
+      </c>
+      <c r="C110" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" t="s">
+        <v>510</v>
+      </c>
+      <c r="E110">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="F110">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="J110">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="K110" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="B111" t="s">
+        <v>527</v>
+      </c>
+      <c r="C111" t="s">
+        <v>31</v>
+      </c>
+      <c r="D111" t="s">
+        <v>510</v>
+      </c>
+      <c r="E111">
+        <v>0.7</v>
+      </c>
+      <c r="F111">
+        <v>0.7</v>
+      </c>
+      <c r="J111">
+        <v>0.7</v>
+      </c>
+      <c r="K111" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
+      <c r="B112" t="s">
+        <v>527</v>
+      </c>
+      <c r="C112" t="s">
+        <v>31</v>
+      </c>
+      <c r="D112" t="s">
+        <v>510</v>
+      </c>
+      <c r="E112">
+        <v>25</v>
+      </c>
+      <c r="F112">
+        <v>25</v>
+      </c>
+      <c r="G112">
+        <v>25</v>
+      </c>
+      <c r="H112">
+        <v>25</v>
+      </c>
+      <c r="I112">
+        <v>25</v>
+      </c>
+      <c r="J112">
+        <v>25</v>
+      </c>
+      <c r="K112" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11">
+      <c r="B113" t="s">
+        <v>527</v>
+      </c>
+      <c r="C113" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" t="s">
+        <v>510</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11">
+      <c r="B114" t="s">
+        <v>527</v>
+      </c>
+      <c r="C114" t="s">
+        <v>31</v>
+      </c>
+      <c r="D114" t="s">
+        <v>510</v>
+      </c>
+      <c r="E114">
+        <v>1.0952</v>
+      </c>
+      <c r="F114">
+        <v>1.0952</v>
+      </c>
+      <c r="G114">
+        <v>1.0952</v>
+      </c>
+      <c r="H114">
+        <v>1.0952</v>
+      </c>
+      <c r="I114">
+        <v>1.0952</v>
+      </c>
+      <c r="J114">
+        <v>1.0952</v>
+      </c>
+      <c r="K114" t="s">
         <v>511</v>
       </c>
-      <c r="D65" t="s">
+    </row>
+    <row r="115" spans="2:11">
+      <c r="B115" t="s">
+        <v>528</v>
+      </c>
+      <c r="C115" t="s">
+        <v>31</v>
+      </c>
+      <c r="D115" t="s">
+        <v>514</v>
+      </c>
+      <c r="E115">
+        <v>5750</v>
+      </c>
+      <c r="F115">
+        <v>5700</v>
+      </c>
+      <c r="J115">
+        <v>5100</v>
+      </c>
+      <c r="K115" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11">
+      <c r="B116" t="s">
+        <v>528</v>
+      </c>
+      <c r="C116" t="s">
+        <v>31</v>
+      </c>
+      <c r="D116" t="s">
+        <v>514</v>
+      </c>
+      <c r="E116">
+        <v>205</v>
+      </c>
+      <c r="F116">
+        <v>200</v>
+      </c>
+      <c r="J116">
+        <v>180</v>
+      </c>
+      <c r="K116" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11">
+      <c r="B117" t="s">
+        <v>528</v>
+      </c>
+      <c r="C117" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" t="s">
+        <v>514</v>
+      </c>
+      <c r="E117">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="F117">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="J117">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="K117" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11">
+      <c r="B118" t="s">
+        <v>528</v>
+      </c>
+      <c r="C118" t="s">
+        <v>31</v>
+      </c>
+      <c r="D118" t="s">
+        <v>514</v>
+      </c>
+      <c r="E118">
+        <v>0.3</v>
+      </c>
+      <c r="F118">
+        <v>0.3</v>
+      </c>
+      <c r="J118">
+        <v>0.3</v>
+      </c>
+      <c r="K118" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11">
+      <c r="B119" t="s">
+        <v>528</v>
+      </c>
+      <c r="C119" t="s">
+        <v>31</v>
+      </c>
+      <c r="D119" t="s">
+        <v>514</v>
+      </c>
+      <c r="E119">
+        <v>0.6</v>
+      </c>
+      <c r="F119">
+        <v>0.6</v>
+      </c>
+      <c r="J119">
+        <v>0.6</v>
+      </c>
+      <c r="K119" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11">
+      <c r="B120" t="s">
+        <v>528</v>
+      </c>
+      <c r="C120" t="s">
+        <v>31</v>
+      </c>
+      <c r="D120" t="s">
+        <v>514</v>
+      </c>
+      <c r="E120">
+        <v>30</v>
+      </c>
+      <c r="F120">
+        <v>30</v>
+      </c>
+      <c r="G120">
+        <v>30</v>
+      </c>
+      <c r="H120">
+        <v>30</v>
+      </c>
+      <c r="I120">
+        <v>30</v>
+      </c>
+      <c r="J120">
+        <v>30</v>
+      </c>
+      <c r="K120" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11">
+      <c r="B121" t="s">
+        <v>528</v>
+      </c>
+      <c r="C121" t="s">
+        <v>31</v>
+      </c>
+      <c r="D121" t="s">
+        <v>514</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+      <c r="F121">
+        <v>3</v>
+      </c>
+      <c r="G121">
+        <v>3</v>
+      </c>
+      <c r="H121">
+        <v>3</v>
+      </c>
+      <c r="I121">
+        <v>3</v>
+      </c>
+      <c r="J121">
+        <v>3</v>
+      </c>
+      <c r="K121" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11">
+      <c r="B122" t="s">
+        <v>529</v>
+      </c>
+      <c r="C122" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" t="s">
         <v>19</v>
       </c>
-      <c r="E65">
-        <v>0.5</v>
-      </c>
-      <c r="F65">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G65">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H65" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="B66" t="s">
-        <v>510</v>
-      </c>
-      <c r="C66" t="s">
-        <v>511</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E122">
+        <v>2850</v>
+      </c>
+      <c r="F122">
+        <v>2750</v>
+      </c>
+      <c r="J122">
+        <v>2550</v>
+      </c>
+      <c r="K122" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11">
+      <c r="B123" t="s">
+        <v>529</v>
+      </c>
+      <c r="C123" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" t="s">
         <v>19</v>
       </c>
-      <c r="E66">
-        <v>3120</v>
-      </c>
-      <c r="F66">
-        <v>2280</v>
-      </c>
-      <c r="G66">
-        <v>1660</v>
-      </c>
-      <c r="H66" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
-      <c r="B67" t="s">
-        <v>510</v>
-      </c>
-      <c r="C67" t="s">
-        <v>511</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="E123">
+        <v>55</v>
+      </c>
+      <c r="F123">
+        <v>55</v>
+      </c>
+      <c r="J123">
+        <v>50</v>
+      </c>
+      <c r="K123" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11">
+      <c r="B124" t="s">
+        <v>529</v>
+      </c>
+      <c r="C124" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" t="s">
         <v>19</v>
       </c>
-      <c r="E67">
-        <v>60</v>
-      </c>
-      <c r="F67">
-        <v>50</v>
-      </c>
-      <c r="G67">
-        <v>40</v>
-      </c>
-      <c r="H67" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8">
-      <c r="B68" t="s">
-        <v>510</v>
-      </c>
-      <c r="C68" t="s">
-        <v>511</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="125" spans="2:11">
+      <c r="B125" t="s">
+        <v>529</v>
+      </c>
+      <c r="C125" t="s">
+        <v>34</v>
+      </c>
+      <c r="D125" t="s">
         <v>19</v>
       </c>
-      <c r="E68">
-        <v>3</v>
-      </c>
-      <c r="F68">
-        <v>3</v>
-      </c>
-      <c r="G68">
-        <v>3</v>
-      </c>
-      <c r="H68" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" t="s">
-        <v>512</v>
-      </c>
-      <c r="C69" t="s">
-        <v>511</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E125">
+        <v>0.1</v>
+      </c>
+      <c r="F125">
+        <v>0.1</v>
+      </c>
+      <c r="J125">
+        <v>0.1</v>
+      </c>
+      <c r="K125" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11">
+      <c r="B126" t="s">
+        <v>529</v>
+      </c>
+      <c r="C126" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" t="s">
         <v>19</v>
       </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8">
-      <c r="B70" t="s">
-        <v>512</v>
-      </c>
-      <c r="C70" t="s">
-        <v>511</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E126">
+        <v>0.85</v>
+      </c>
+      <c r="F126">
+        <v>0.85</v>
+      </c>
+      <c r="J126">
+        <v>0.85</v>
+      </c>
+      <c r="K126" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11">
+      <c r="B127" t="s">
+        <v>529</v>
+      </c>
+      <c r="C127" t="s">
+        <v>34</v>
+      </c>
+      <c r="D127" t="s">
         <v>19</v>
       </c>
-      <c r="E70">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="F70">
-        <v>0.3</v>
-      </c>
-      <c r="G70">
-        <v>0.3</v>
-      </c>
-      <c r="H70" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
-      <c r="B71" t="s">
-        <v>512</v>
-      </c>
-      <c r="C71" t="s">
-        <v>511</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="E127">
+        <v>30</v>
+      </c>
+      <c r="F127">
+        <v>30</v>
+      </c>
+      <c r="G127">
+        <v>30</v>
+      </c>
+      <c r="H127">
+        <v>30</v>
+      </c>
+      <c r="I127">
+        <v>30</v>
+      </c>
+      <c r="J127">
+        <v>30</v>
+      </c>
+      <c r="K127" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="128" spans="2:11">
+      <c r="B128" t="s">
+        <v>529</v>
+      </c>
+      <c r="C128" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" t="s">
         <v>19</v>
       </c>
-      <c r="E71">
-        <v>1630</v>
-      </c>
-      <c r="F71">
-        <v>1550</v>
-      </c>
-      <c r="G71">
-        <v>1490</v>
-      </c>
-      <c r="H71" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8">
-      <c r="B72" t="s">
-        <v>512</v>
-      </c>
-      <c r="C72" t="s">
-        <v>511</v>
-      </c>
-      <c r="D72" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72">
-        <v>42</v>
-      </c>
-      <c r="F72">
-        <v>40</v>
-      </c>
-      <c r="G72">
-        <v>38</v>
-      </c>
-      <c r="H72" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
-        <v>512</v>
-      </c>
-      <c r="C73" t="s">
-        <v>511</v>
-      </c>
-      <c r="D73" t="s">
-        <v>19</v>
-      </c>
-      <c r="E73">
-        <v>1.5</v>
-      </c>
-      <c r="F73">
-        <v>1.5</v>
-      </c>
-      <c r="G73">
-        <v>1.5</v>
-      </c>
-      <c r="H73" t="s">
-        <v>495</v>
+      <c r="E128">
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <v>4</v>
+      </c>
+      <c r="G128">
+        <v>4</v>
+      </c>
+      <c r="H128">
+        <v>4</v>
+      </c>
+      <c r="I128">
+        <v>4</v>
+      </c>
+      <c r="J128">
+        <v>4</v>
+      </c>
+      <c r="K128" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
